--- a/src/main/resources/2025年10月度UNISS勤務表(〇〇).xlsx
+++ b/src/main/resources/2025年10月度UNISS勤務表(〇〇).xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10102"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Dropbox\00.SyncFolder\22.勤務表\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/akihirokakutani/Documents/GitHub/Kotlin_SpringBoot/src/main/resources/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3911D91-EFB3-47C0-B69B-15507D498DCA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0D47118-4F28-934A-AF7E-DCDA7419FAD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{5FD4C467-C22C-E24D-BDF3-40761EFBB2C5}"/>
+    <workbookView xWindow="0" yWindow="620" windowWidth="29040" windowHeight="15720" xr2:uid="{5FD4C467-C22C-E24D-BDF3-40761EFBB2C5}"/>
   </bookViews>
   <sheets>
     <sheet name="ユーニス勤務表2025改良版" sheetId="4" r:id="rId1"/>
@@ -23,6 +23,16 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -65,14 +75,14 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
   <futureMetadata name="XLDAPR" count="1">
     <bk>
       <extLst>
-        <ext xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray" uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
           <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
         </ext>
       </extLst>
@@ -1351,42 +1361,12 @@
     <xf numFmtId="0" fontId="8" fillId="3" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="4" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="4" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="6" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="6" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="17" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="distributed" textRotation="255" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="20" fontId="7" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" shrinkToFit="1"/>
     </xf>
@@ -1396,9 +1376,6 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
@@ -1408,42 +1385,15 @@
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="20" fontId="19" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="16" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="18" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous" vertical="center"/>
     </xf>
@@ -1486,24 +1436,9 @@
     <xf numFmtId="0" fontId="17" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="26" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="distributed" textRotation="255" wrapText="1" shrinkToFit="1"/>
     </xf>
@@ -1537,7 +1472,7 @@
     <xf numFmtId="0" fontId="29" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="29" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1546,11 +1481,86 @@
     <xf numFmtId="0" fontId="30" fillId="0" borderId="13" xfId="2" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="30" fillId="7" borderId="13" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="30" fillId="8" borderId="13" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="6" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="6" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1914,168 +1924,168 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:AS45"/>
-  <sheetFormatPr defaultColWidth="7.5546875" defaultRowHeight="18.75"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="7.5703125" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="1.44140625" style="1" customWidth="1"/>
-    <col min="2" max="8" width="3.33203125" style="1" customWidth="1"/>
-    <col min="9" max="10" width="4.77734375" style="1" customWidth="1"/>
-    <col min="11" max="13" width="5.77734375" style="1" customWidth="1"/>
-    <col min="14" max="21" width="3.33203125" style="1" customWidth="1"/>
-    <col min="22" max="27" width="5.77734375" style="1" customWidth="1"/>
-    <col min="28" max="28" width="22.109375" style="1" customWidth="1"/>
-    <col min="29" max="38" width="5.77734375" style="1" customWidth="1"/>
+    <col min="1" max="1" width="1.42578125" style="1" customWidth="1"/>
+    <col min="2" max="8" width="3.28515625" style="1" customWidth="1"/>
+    <col min="9" max="10" width="4.7109375" style="1" customWidth="1"/>
+    <col min="11" max="13" width="5.7109375" style="1" customWidth="1"/>
+    <col min="14" max="21" width="3.28515625" style="1" customWidth="1"/>
+    <col min="22" max="27" width="5.7109375" style="1" customWidth="1"/>
+    <col min="28" max="28" width="22.140625" style="1" customWidth="1"/>
+    <col min="29" max="38" width="5.7109375" style="1" customWidth="1"/>
     <col min="39" max="39" width="4" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="41" width="5.77734375" style="1" customWidth="1"/>
-    <col min="42" max="42" width="2.109375" style="1" customWidth="1"/>
-    <col min="43" max="43" width="2.6640625" style="1" customWidth="1"/>
-    <col min="44" max="44" width="9.33203125" style="1" customWidth="1"/>
-    <col min="45" max="45" width="5.88671875" style="1" customWidth="1"/>
-    <col min="46" max="138" width="2.109375" style="1" customWidth="1"/>
-    <col min="139" max="16384" width="7.5546875" style="1"/>
+    <col min="40" max="41" width="5.7109375" style="1" customWidth="1"/>
+    <col min="42" max="42" width="2.140625" style="1" customWidth="1"/>
+    <col min="43" max="43" width="2.7109375" style="1" customWidth="1"/>
+    <col min="44" max="44" width="9.28515625" style="1" customWidth="1"/>
+    <col min="45" max="45" width="5.85546875" style="1" customWidth="1"/>
+    <col min="46" max="138" width="2.140625" style="1" customWidth="1"/>
+    <col min="139" max="16384" width="7.5703125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:45" ht="5.0999999999999996" customHeight="1"/>
-    <row r="2" spans="2:45" ht="27.95" customHeight="1">
-      <c r="B2" s="65" t="s">
+    <row r="1" spans="2:45" ht="5" customHeight="1"/>
+    <row r="2" spans="2:45" ht="28" customHeight="1">
+      <c r="B2" s="90" t="s">
         <v>69</v>
       </c>
-      <c r="C2" s="66"/>
-      <c r="D2" s="52"/>
-      <c r="E2" s="93"/>
-      <c r="F2" s="93"/>
-      <c r="G2" s="93"/>
-      <c r="H2" s="54"/>
-      <c r="I2" s="53"/>
-      <c r="J2" s="93"/>
-      <c r="K2" s="54"/>
-      <c r="M2" s="58">
+      <c r="C2" s="91"/>
+      <c r="D2" s="111"/>
+      <c r="E2" s="103"/>
+      <c r="F2" s="103"/>
+      <c r="G2" s="103"/>
+      <c r="H2" s="104"/>
+      <c r="I2" s="102"/>
+      <c r="J2" s="103"/>
+      <c r="K2" s="104"/>
+      <c r="M2" s="101">
         <v>2025</v>
       </c>
-      <c r="N2" s="58"/>
-      <c r="O2" s="62">
+      <c r="N2" s="101"/>
+      <c r="O2" s="85">
         <v>12</v>
       </c>
-      <c r="P2" s="62"/>
-      <c r="Q2" s="59" t="s">
+      <c r="P2" s="85"/>
+      <c r="Q2" s="48" t="s">
         <v>1</v>
       </c>
-      <c r="R2" s="61"/>
-      <c r="S2" s="60"/>
-      <c r="T2" s="60"/>
-      <c r="U2" s="60"/>
-      <c r="V2" s="60"/>
-      <c r="W2" s="60"/>
-      <c r="X2" s="60"/>
-      <c r="Y2" s="60"/>
-      <c r="Z2" s="60"/>
-      <c r="AA2" s="60"/>
+      <c r="R2" s="50"/>
+      <c r="S2" s="49"/>
+      <c r="T2" s="49"/>
+      <c r="U2" s="49"/>
+      <c r="V2" s="49"/>
+      <c r="W2" s="49"/>
+      <c r="X2" s="49"/>
+      <c r="Y2" s="49"/>
+      <c r="Z2" s="49"/>
+      <c r="AA2" s="49"/>
       <c r="AB2" s="3" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="3" spans="2:45" ht="27.95" customHeight="1">
-      <c r="B3" s="67"/>
-      <c r="C3" s="68"/>
-      <c r="D3" s="70" t="s">
+    <row r="3" spans="2:45" ht="28" customHeight="1">
+      <c r="B3" s="92"/>
+      <c r="C3" s="93"/>
+      <c r="D3" s="105" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="71"/>
-      <c r="F3" s="72"/>
-      <c r="G3" s="88"/>
-      <c r="H3" s="89"/>
-      <c r="I3" s="73" t="s">
+      <c r="E3" s="106"/>
+      <c r="F3" s="107"/>
+      <c r="G3" s="109"/>
+      <c r="H3" s="110"/>
+      <c r="I3" s="108" t="s">
         <v>4</v>
       </c>
-      <c r="J3" s="71"/>
-      <c r="K3" s="90"/>
-      <c r="L3" s="110" t="s">
+      <c r="J3" s="106"/>
+      <c r="K3" s="68"/>
+      <c r="L3" s="88" t="s">
         <v>81</v>
       </c>
-      <c r="M3" s="111"/>
-      <c r="N3" s="111"/>
-      <c r="O3" s="111"/>
-      <c r="P3" s="111"/>
-      <c r="Q3" s="111"/>
-      <c r="R3" s="111"/>
-      <c r="S3" s="111"/>
-      <c r="T3" s="111"/>
-      <c r="U3" s="111"/>
-      <c r="V3" s="111"/>
-      <c r="W3" s="111"/>
-      <c r="X3" s="111"/>
-      <c r="Y3" s="111"/>
-      <c r="Z3" s="111"/>
-      <c r="AA3" s="111"/>
+      <c r="M3" s="89"/>
+      <c r="N3" s="89"/>
+      <c r="O3" s="89"/>
+      <c r="P3" s="89"/>
+      <c r="Q3" s="89"/>
+      <c r="R3" s="89"/>
+      <c r="S3" s="89"/>
+      <c r="T3" s="89"/>
+      <c r="U3" s="89"/>
+      <c r="V3" s="89"/>
+      <c r="W3" s="89"/>
+      <c r="X3" s="89"/>
+      <c r="Y3" s="89"/>
+      <c r="Z3" s="89"/>
+      <c r="AA3" s="89"/>
     </row>
-    <row r="4" spans="2:45" ht="27.95" customHeight="1">
-      <c r="B4" s="91" t="s">
+    <row r="4" spans="2:45" ht="28" customHeight="1">
+      <c r="B4" s="86" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="92"/>
-      <c r="D4" s="43"/>
-      <c r="E4" s="44"/>
-      <c r="F4" s="44"/>
-      <c r="G4" s="74" t="s">
+      <c r="C4" s="87"/>
+      <c r="D4" s="94"/>
+      <c r="E4" s="95"/>
+      <c r="F4" s="95"/>
+      <c r="G4" s="54" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="69"/>
-      <c r="I4" s="74"/>
-      <c r="J4" s="45">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="K4" s="46"/>
-      <c r="L4" s="110"/>
-      <c r="M4" s="111"/>
-      <c r="N4" s="111"/>
-      <c r="O4" s="111"/>
-      <c r="P4" s="111"/>
-      <c r="Q4" s="111"/>
-      <c r="R4" s="111"/>
-      <c r="S4" s="111"/>
-      <c r="T4" s="111"/>
-      <c r="U4" s="111"/>
-      <c r="V4" s="111"/>
-      <c r="W4" s="111"/>
-      <c r="X4" s="111"/>
-      <c r="Y4" s="111"/>
-      <c r="Z4" s="111"/>
-      <c r="AA4" s="111"/>
+      <c r="H4" s="53"/>
+      <c r="I4" s="54"/>
+      <c r="J4" s="96">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="K4" s="97"/>
+      <c r="L4" s="88"/>
+      <c r="M4" s="89"/>
+      <c r="N4" s="89"/>
+      <c r="O4" s="89"/>
+      <c r="P4" s="89"/>
+      <c r="Q4" s="89"/>
+      <c r="R4" s="89"/>
+      <c r="S4" s="89"/>
+      <c r="T4" s="89"/>
+      <c r="U4" s="89"/>
+      <c r="V4" s="89"/>
+      <c r="W4" s="89"/>
+      <c r="X4" s="89"/>
+      <c r="Y4" s="89"/>
+      <c r="Z4" s="89"/>
+      <c r="AA4" s="89"/>
       <c r="AN4" s="2"/>
     </row>
-    <row r="5" spans="2:45" ht="27.95" customHeight="1">
-      <c r="B5" s="69" t="s">
+    <row r="5" spans="2:45" ht="28" customHeight="1">
+      <c r="B5" s="53" t="s">
         <v>74</v>
       </c>
-      <c r="C5" s="69"/>
-      <c r="D5" s="47"/>
-      <c r="E5" s="48"/>
-      <c r="F5" s="48"/>
-      <c r="G5" s="48"/>
-      <c r="H5" s="48"/>
-      <c r="I5" s="48"/>
-      <c r="J5" s="48"/>
-      <c r="K5" s="49"/>
-      <c r="L5" s="110"/>
-      <c r="M5" s="111"/>
-      <c r="N5" s="111"/>
-      <c r="O5" s="111"/>
-      <c r="P5" s="111"/>
-      <c r="Q5" s="111"/>
-      <c r="R5" s="111"/>
-      <c r="S5" s="111"/>
-      <c r="T5" s="111"/>
-      <c r="U5" s="111"/>
-      <c r="V5" s="111"/>
-      <c r="W5" s="111"/>
-      <c r="X5" s="111"/>
-      <c r="Y5" s="111"/>
-      <c r="Z5" s="111"/>
-      <c r="AA5" s="111"/>
+      <c r="C5" s="53"/>
+      <c r="D5" s="98"/>
+      <c r="E5" s="99"/>
+      <c r="F5" s="99"/>
+      <c r="G5" s="99"/>
+      <c r="H5" s="99"/>
+      <c r="I5" s="99"/>
+      <c r="J5" s="99"/>
+      <c r="K5" s="100"/>
+      <c r="L5" s="88"/>
+      <c r="M5" s="89"/>
+      <c r="N5" s="89"/>
+      <c r="O5" s="89"/>
+      <c r="P5" s="89"/>
+      <c r="Q5" s="89"/>
+      <c r="R5" s="89"/>
+      <c r="S5" s="89"/>
+      <c r="T5" s="89"/>
+      <c r="U5" s="89"/>
+      <c r="V5" s="89"/>
+      <c r="W5" s="89"/>
+      <c r="X5" s="89"/>
+      <c r="Y5" s="89"/>
+      <c r="Z5" s="89"/>
+      <c r="AA5" s="89"/>
       <c r="AD5" s="4"/>
       <c r="AN5" s="2"/>
     </row>
-    <row r="6" spans="2:45" ht="5.0999999999999996" customHeight="1"/>
-    <row r="7" spans="2:45" s="16" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="6" spans="2:45" ht="5" customHeight="1"/>
+    <row r="7" spans="2:45" s="16" customFormat="1" ht="20" customHeight="1">
       <c r="B7" s="5"/>
       <c r="C7" s="6"/>
       <c r="D7" s="6"/>
@@ -2106,70 +2116,70 @@
       <c r="Y7" s="11"/>
       <c r="Z7" s="11"/>
       <c r="AA7" s="12"/>
-      <c r="AB7" s="51" t="s">
+      <c r="AB7" s="44" t="s">
         <v>6</v>
       </c>
-      <c r="AC7" s="97" t="s">
+      <c r="AC7" s="72" t="s">
         <v>8</v>
       </c>
-      <c r="AD7" s="98"/>
-      <c r="AE7" s="98"/>
-      <c r="AF7" s="98"/>
-      <c r="AG7" s="98"/>
-      <c r="AH7" s="98"/>
-      <c r="AI7" s="98"/>
-      <c r="AJ7" s="98"/>
-      <c r="AK7" s="98"/>
-      <c r="AL7" s="98"/>
-      <c r="AM7" s="98"/>
-      <c r="AN7" s="98"/>
-      <c r="AO7" s="99"/>
+      <c r="AD7" s="73"/>
+      <c r="AE7" s="73"/>
+      <c r="AF7" s="73"/>
+      <c r="AG7" s="73"/>
+      <c r="AH7" s="73"/>
+      <c r="AI7" s="73"/>
+      <c r="AJ7" s="73"/>
+      <c r="AK7" s="73"/>
+      <c r="AL7" s="73"/>
+      <c r="AM7" s="73"/>
+      <c r="AN7" s="73"/>
+      <c r="AO7" s="74"/>
     </row>
-    <row r="8" spans="2:45" s="16" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="8" spans="2:45" s="16" customFormat="1" ht="20" customHeight="1">
       <c r="B8" s="17"/>
       <c r="C8" s="18"/>
       <c r="D8" s="18"/>
-      <c r="E8" s="75" t="s">
+      <c r="E8" s="55" t="s">
         <v>70</v>
       </c>
-      <c r="F8" s="76"/>
-      <c r="G8" s="77" t="s">
+      <c r="F8" s="56"/>
+      <c r="G8" s="57" t="s">
         <v>71</v>
       </c>
-      <c r="H8" s="76"/>
-      <c r="I8" s="78" t="s">
-        <v>0</v>
-      </c>
-      <c r="J8" s="79"/>
-      <c r="K8" s="96" t="s">
+      <c r="H8" s="56"/>
+      <c r="I8" s="58" t="s">
+        <v>0</v>
+      </c>
+      <c r="J8" s="59"/>
+      <c r="K8" s="71" t="s">
         <v>77</v>
       </c>
-      <c r="L8" s="80"/>
-      <c r="M8" s="80"/>
-      <c r="N8" s="81" t="s">
+      <c r="L8" s="60"/>
+      <c r="M8" s="60"/>
+      <c r="N8" s="61" t="s">
         <v>72</v>
       </c>
-      <c r="O8" s="80"/>
-      <c r="P8" s="75" t="s">
+      <c r="O8" s="60"/>
+      <c r="P8" s="55" t="s">
         <v>78</v>
       </c>
-      <c r="Q8" s="80"/>
-      <c r="R8" s="80"/>
-      <c r="S8" s="80"/>
-      <c r="T8" s="80"/>
-      <c r="U8" s="76"/>
-      <c r="V8" s="82" t="s">
+      <c r="Q8" s="60"/>
+      <c r="R8" s="60"/>
+      <c r="S8" s="60"/>
+      <c r="T8" s="60"/>
+      <c r="U8" s="56"/>
+      <c r="V8" s="62" t="s">
         <v>9</v>
       </c>
-      <c r="W8" s="83" t="s">
+      <c r="W8" s="63" t="s">
         <v>10</v>
       </c>
-      <c r="X8" s="84"/>
-      <c r="Y8" s="85"/>
-      <c r="Z8" s="83" t="s">
+      <c r="X8" s="64"/>
+      <c r="Y8" s="65"/>
+      <c r="Z8" s="63" t="s">
         <v>11</v>
       </c>
-      <c r="AA8" s="85"/>
+      <c r="AA8" s="65"/>
       <c r="AB8" s="41"/>
       <c r="AC8" s="13" t="s">
         <v>12</v>
@@ -2187,7 +2197,7 @@
       <c r="AN8" s="14"/>
       <c r="AO8" s="15"/>
     </row>
-    <row r="9" spans="2:45" ht="62.1" customHeight="1">
+    <row r="9" spans="2:45" ht="62" customHeight="1">
       <c r="B9" s="19" t="s">
         <v>13</v>
       </c>
@@ -2209,103 +2219,103 @@
       <c r="H9" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="I9" s="94" t="s">
+      <c r="I9" s="69" t="s">
         <v>17</v>
       </c>
-      <c r="J9" s="94" t="s">
+      <c r="J9" s="69" t="s">
         <v>18</v>
       </c>
-      <c r="K9" s="94" t="s">
+      <c r="K9" s="69" t="s">
         <v>19</v>
       </c>
-      <c r="L9" s="94" t="s">
+      <c r="L9" s="69" t="s">
         <v>20</v>
       </c>
-      <c r="M9" s="94" t="s">
+      <c r="M9" s="69" t="s">
         <v>21</v>
       </c>
-      <c r="N9" s="50" t="s">
+      <c r="N9" s="43" t="s">
         <v>73</v>
       </c>
-      <c r="O9" s="50" t="s">
+      <c r="O9" s="43" t="s">
         <v>22</v>
       </c>
-      <c r="P9" s="87" t="s">
+      <c r="P9" s="67" t="s">
         <v>23</v>
       </c>
-      <c r="Q9" s="87" t="s">
+      <c r="Q9" s="67" t="s">
         <v>24</v>
       </c>
-      <c r="R9" s="50" t="s">
+      <c r="R9" s="43" t="s">
         <v>25</v>
       </c>
-      <c r="S9" s="87" t="s">
+      <c r="S9" s="67" t="s">
         <v>26</v>
       </c>
-      <c r="T9" s="87" t="s">
+      <c r="T9" s="67" t="s">
         <v>27</v>
       </c>
-      <c r="U9" s="87" t="s">
+      <c r="U9" s="67" t="s">
         <v>28</v>
       </c>
-      <c r="V9" s="86" t="s">
+      <c r="V9" s="66" t="s">
         <v>29</v>
       </c>
-      <c r="W9" s="86" t="s">
+      <c r="W9" s="66" t="s">
         <v>30</v>
       </c>
-      <c r="X9" s="86" t="s">
+      <c r="X9" s="66" t="s">
         <v>31</v>
       </c>
-      <c r="Y9" s="86" t="s">
+      <c r="Y9" s="66" t="s">
         <v>32</v>
       </c>
-      <c r="Z9" s="86" t="s">
+      <c r="Z9" s="66" t="s">
         <v>33</v>
       </c>
-      <c r="AA9" s="86" t="s">
+      <c r="AA9" s="66" t="s">
         <v>34</v>
       </c>
       <c r="AB9" s="42" t="s">
         <v>35</v>
       </c>
-      <c r="AC9" s="100" t="s">
+      <c r="AC9" s="75" t="s">
         <v>36</v>
       </c>
-      <c r="AD9" s="100" t="s">
+      <c r="AD9" s="75" t="s">
         <v>37</v>
       </c>
-      <c r="AE9" s="100" t="s">
+      <c r="AE9" s="75" t="s">
         <v>38</v>
       </c>
-      <c r="AF9" s="100" t="s">
+      <c r="AF9" s="75" t="s">
         <v>39</v>
       </c>
-      <c r="AG9" s="100" t="s">
+      <c r="AG9" s="75" t="s">
         <v>40</v>
       </c>
-      <c r="AH9" s="100" t="s">
+      <c r="AH9" s="75" t="s">
         <v>41</v>
       </c>
-      <c r="AI9" s="100" t="s">
+      <c r="AI9" s="75" t="s">
         <v>42</v>
       </c>
-      <c r="AJ9" s="100" t="s">
+      <c r="AJ9" s="75" t="s">
         <v>43</v>
       </c>
-      <c r="AK9" s="100" t="s">
+      <c r="AK9" s="75" t="s">
         <v>44</v>
       </c>
-      <c r="AL9" s="100" t="s">
+      <c r="AL9" s="75" t="s">
         <v>45</v>
       </c>
-      <c r="AM9" s="101" t="s">
+      <c r="AM9" s="76" t="s">
         <v>46</v>
       </c>
-      <c r="AN9" s="102" t="s">
+      <c r="AN9" s="77" t="s">
         <v>79</v>
       </c>
-      <c r="AO9" s="102" t="s">
+      <c r="AO9" s="77" t="s">
         <v>80</v>
       </c>
       <c r="AR9" s="21" t="s">
@@ -2315,14 +2325,14 @@
     </row>
     <row r="10" spans="2:45" ht="15" customHeight="1">
       <c r="B10" s="23">
-        <f>IFERROR(IF(OR(COUNTIF($AR$11:$AR$40, C10)&gt;0, WEEKDAY(C10, 2)&gt;5), 0, 1), "")</f>
+        <f>IFERROR(IF(OR(COUNTIF($AR$10:$AR$40, C10)&gt;0, WEEKDAY(C10, 2)&gt;5), 0, 1), "")</f>
         <v>1</v>
       </c>
       <c r="C10" s="24">
         <f>DATE(M2, O2, 1)</f>
         <v>45992</v>
       </c>
-      <c r="D10" s="57" t="str">
+      <c r="D10" s="47" t="str">
         <f>IF(C10&lt;&gt;"", CHOOSE(WEEKDAY(C10), "日", "月", "火", "水", "木", "金", "土"), "")</f>
         <v>月</v>
       </c>
@@ -2370,77 +2380,73 @@
         <f t="shared" ref="AA10" si="1">IF(OR(AM10=0, AND(L10="", M10="")), "", L10+M10)</f>
         <v/>
       </c>
-      <c r="AB10" s="55"/>
-      <c r="AC10" s="56">
+      <c r="AB10" s="45"/>
+      <c r="AC10" s="46">
         <f t="shared" ref="AC10:AC40" si="2">E10/24 + F10/1440</f>
         <v>0</v>
       </c>
-      <c r="AD10" s="56">
+      <c r="AD10" s="46">
         <f t="shared" ref="AD10:AD40" si="3">G10/24 + H10/1440</f>
         <v>0</v>
       </c>
-      <c r="AE10" s="56">
+      <c r="AE10" s="46">
         <f>IF(AD10&lt;AC10,AD10+1,AD10)-AC10</f>
         <v>0</v>
       </c>
-      <c r="AF10" s="56">
+      <c r="AF10" s="46">
         <f t="shared" ref="AF10:AF40" si="4">TIME(0,I10+J10,0)</f>
         <v>0</v>
       </c>
-      <c r="AG10" s="56">
+      <c r="AG10" s="46">
         <f t="shared" ref="AG10:AG40" si="5">IF(AE10 - AF10 &lt; TIME(0, 0, 0), TIME(0, 0, 0), AE10 - AF10)</f>
         <v>0</v>
       </c>
-      <c r="AH10" s="56">
+      <c r="AH10" s="46">
         <f t="shared" ref="AH10:AH40" si="6">IF(AO10 &lt; AG10, AG10  - AO10, TIME(0,0,0))</f>
         <v>0</v>
       </c>
-      <c r="AI10" s="56">
+      <c r="AI10" s="46">
         <f>IF(U10="○","0:00",IF(AH10&gt;TIME(4,0,0),TIME(4,0,0),AH10))</f>
         <v>0</v>
       </c>
-      <c r="AJ10" s="56">
+      <c r="AJ10" s="46">
         <f>IF(S10="○", TIME(0,0,0), IF(AG10&gt;TIME(19,0,0), AG10-TIME(19,0,0), TIME(0,0,0)))</f>
         <v>0</v>
       </c>
-      <c r="AK10" s="56">
+      <c r="AK10" s="46">
         <f t="shared" ref="AK10:AK40" si="7">IF(AG10&gt;TIME(12,0,0), MIN(AG10-TIME(12,0,0), TIME(7,0,0)), TIME(0,0,0))</f>
         <v>0</v>
       </c>
-      <c r="AL10" s="56">
+      <c r="AL10" s="46">
         <f>IF(U10="○", AG10,TIME(0,0,0))</f>
         <v>0</v>
       </c>
-      <c r="AM10" s="63">
+      <c r="AM10" s="51">
         <f t="shared" ref="AM10:AM40" si="8">IF(AND(E10&lt;&gt;"", F10&lt;&gt;"", G10&lt;&gt;"", H10&lt;&gt;""), 1, IF(R10="○", 1, 0))</f>
         <v>0</v>
       </c>
-      <c r="AN10" s="64">
+      <c r="AN10" s="52">
         <f xml:space="preserve"> $J$4-SUM(IF(K10&lt;&gt;"",TEXT("4:00","h:mm"),K10),L10,M10)</f>
         <v>0.33333333333333331</v>
       </c>
-      <c r="AO10" s="64">
+      <c r="AO10" s="52">
         <f>TIME(8,0,0)-SUM(IF(K10&lt;&gt;"",TEXT("4:00","h:mm"),K10),L10,M10)</f>
         <v>0.33333333333333331</v>
       </c>
       <c r="AQ10" s="1">
         <v>1</v>
-      </c>
-      <c r="AR10" s="1" t="str">
-        <f>IF(M$2="", "年度を入力してください", IFERROR(_xlfn.WEBSERVICE("https://api.excelapi.org/datetime/holiday-list?year="&amp;M$2&amp;"&amp;line="&amp;$AQ10), "祝日が読み取れません。手入力でお願いします。"))</f>
-        <v>2025/1/1</v>
       </c>
     </row>
     <row r="11" spans="2:45" ht="15" customHeight="1">
       <c r="B11" s="23">
-        <f t="shared" ref="B11:B40" si="9">IFERROR(IF(OR(COUNTIF($AR$11:$AR$40, C11)&gt;0, WEEKDAY(C11, 2)&gt;5), 0, 1), "")</f>
+        <f t="shared" ref="B11:B40" si="9">IFERROR(IF(OR(COUNTIF($AR$10:$AR$40, C11)&gt;0, WEEKDAY(C11, 2)&gt;5), 0, 1), "")</f>
         <v>1</v>
       </c>
       <c r="C11" s="24">
         <f>IFERROR(IF(AND(ISNUMBER(C10), MONTH(C10+1) = MONTH($C$10), C10+1 &lt;= EOMONTH($C$10, 0)), C10+1, ""), "")</f>
         <v>45993</v>
       </c>
-      <c r="D11" s="57" t="str">
+      <c r="D11" s="47" t="str">
         <f t="shared" ref="D11:D40" si="10">IF(C11&lt;&gt;"", CHOOSE(WEEKDAY(C11), "日", "月", "火", "水", "木", "金", "土"), "")</f>
         <v>火</v>
       </c>
@@ -2488,65 +2494,61 @@
         <f t="shared" ref="AA11:AA40" si="16">IF(OR(AM11=0, AND(L11="", M11="")), "", L11+M11)</f>
         <v/>
       </c>
-      <c r="AB11" s="55"/>
-      <c r="AC11" s="56">
+      <c r="AB11" s="45"/>
+      <c r="AC11" s="46">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AD11" s="56">
+      <c r="AD11" s="46">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AE11" s="56">
+      <c r="AE11" s="46">
         <f t="shared" ref="AE11:AE40" si="17">IF(AD11&lt;AC11,AD11+1,AD11)-AC11</f>
         <v>0</v>
       </c>
-      <c r="AF11" s="56">
+      <c r="AF11" s="46">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AG11" s="56">
+      <c r="AG11" s="46">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AH11" s="56">
+      <c r="AH11" s="46">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AI11" s="56">
+      <c r="AI11" s="46">
         <f t="shared" ref="AI11:AI40" si="18">IF(U11="○","0:00",IF(AH11&gt;TIME(4,0,0),TIME(4,0,0),AH11))</f>
         <v>0</v>
       </c>
-      <c r="AJ11" s="56">
+      <c r="AJ11" s="46">
         <f t="shared" ref="AJ11:AJ40" si="19">IF(S11="○", TIME(0,0,0), IF(AG11&gt;TIME(19,0,0), AG11-TIME(19,0,0), TIME(0,0,0)))</f>
         <v>0</v>
       </c>
-      <c r="AK11" s="56">
+      <c r="AK11" s="46">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AL11" s="56">
+      <c r="AL11" s="46">
         <f t="shared" ref="AL11:AL40" si="20">IF(U11="○", AG11,TIME(0,0,0))</f>
         <v>0</v>
       </c>
-      <c r="AM11" s="63">
+      <c r="AM11" s="51">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AN11" s="64">
+      <c r="AN11" s="52">
         <f t="shared" ref="AN11:AN40" si="21" xml:space="preserve"> $J$4-SUM(IF(K11&lt;&gt;"",TEXT("4:00","h:mm"),K11),L11,M11)</f>
         <v>0.33333333333333331</v>
       </c>
-      <c r="AO11" s="64">
+      <c r="AO11" s="52">
         <f t="shared" ref="AO11:AO40" si="22">TIME(8,0,0)-SUM(IF(K11&lt;&gt;"",TEXT("4:00","h:mm"),K11),L11,M11)</f>
         <v>0.33333333333333331</v>
       </c>
       <c r="AQ11" s="1">
         <v>2</v>
-      </c>
-      <c r="AR11" s="1" t="str">
-        <f t="shared" ref="AR11:AR40" si="23">IF(M$2="", "", IFERROR(_xlfn.WEBSERVICE("https://api.excelapi.org/datetime/holiday-list?year="&amp;M$2&amp;"&amp;line="&amp;$AQ11), ""))</f>
-        <v>2025/1/13</v>
       </c>
     </row>
     <row r="12" spans="2:45" ht="15" customHeight="1">
@@ -2555,10 +2557,10 @@
         <v>1</v>
       </c>
       <c r="C12" s="24">
-        <f t="shared" ref="C12:C39" si="24">IFERROR(IF(AND(ISNUMBER(C11), MONTH(C11+1) = MONTH($C$10), C11+1 &lt;= EOMONTH($C$10, 0)), C11+1, ""), "")</f>
+        <f t="shared" ref="C12:C39" si="23">IFERROR(IF(AND(ISNUMBER(C11), MONTH(C11+1) = MONTH($C$10), C11+1 &lt;= EOMONTH($C$10, 0)), C11+1, ""), "")</f>
         <v>45994</v>
       </c>
-      <c r="D12" s="57" t="str">
+      <c r="D12" s="47" t="str">
         <f t="shared" si="10"/>
         <v>水</v>
       </c>
@@ -2606,65 +2608,61 @@
         <f t="shared" si="16"/>
         <v/>
       </c>
-      <c r="AB12" s="55"/>
-      <c r="AC12" s="56">
+      <c r="AB12" s="45"/>
+      <c r="AC12" s="46">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AD12" s="56">
+      <c r="AD12" s="46">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AE12" s="56">
+      <c r="AE12" s="46">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="AF12" s="56">
+      <c r="AF12" s="46">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AG12" s="56">
+      <c r="AG12" s="46">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AH12" s="56">
+      <c r="AH12" s="46">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AI12" s="56">
+      <c r="AI12" s="46">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="AJ12" s="56">
+      <c r="AJ12" s="46">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="AK12" s="56">
+      <c r="AK12" s="46">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AL12" s="56">
+      <c r="AL12" s="46">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="AM12" s="63">
+      <c r="AM12" s="51">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AN12" s="64">
+      <c r="AN12" s="52">
         <f t="shared" si="21"/>
         <v>0.33333333333333331</v>
       </c>
-      <c r="AO12" s="64">
+      <c r="AO12" s="52">
         <f t="shared" si="22"/>
         <v>0.33333333333333331</v>
       </c>
       <c r="AQ12" s="1">
         <v>3</v>
-      </c>
-      <c r="AR12" s="1" t="str">
-        <f t="shared" si="23"/>
-        <v>2025/2/11</v>
       </c>
     </row>
     <row r="13" spans="2:45" ht="15" customHeight="1">
@@ -2673,10 +2671,10 @@
         <v>1</v>
       </c>
       <c r="C13" s="24">
-        <f t="shared" si="24"/>
+        <f t="shared" si="23"/>
         <v>45995</v>
       </c>
-      <c r="D13" s="57" t="str">
+      <c r="D13" s="47" t="str">
         <f t="shared" si="10"/>
         <v>木</v>
       </c>
@@ -2724,65 +2722,61 @@
         <f t="shared" si="16"/>
         <v/>
       </c>
-      <c r="AB13" s="55"/>
-      <c r="AC13" s="56">
+      <c r="AB13" s="45"/>
+      <c r="AC13" s="46">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AD13" s="56">
+      <c r="AD13" s="46">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AE13" s="56">
+      <c r="AE13" s="46">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="AF13" s="56">
+      <c r="AF13" s="46">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AG13" s="56">
+      <c r="AG13" s="46">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AH13" s="56">
+      <c r="AH13" s="46">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AI13" s="56">
+      <c r="AI13" s="46">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="AJ13" s="56">
+      <c r="AJ13" s="46">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="AK13" s="56">
+      <c r="AK13" s="46">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AL13" s="56">
+      <c r="AL13" s="46">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="AM13" s="63">
+      <c r="AM13" s="51">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AN13" s="64">
+      <c r="AN13" s="52">
         <f t="shared" si="21"/>
         <v>0.33333333333333331</v>
       </c>
-      <c r="AO13" s="64">
+      <c r="AO13" s="52">
         <f t="shared" si="22"/>
         <v>0.33333333333333331</v>
       </c>
       <c r="AQ13" s="1">
         <v>4</v>
-      </c>
-      <c r="AR13" s="1" t="str">
-        <f t="shared" si="23"/>
-        <v>2025/2/23</v>
       </c>
     </row>
     <row r="14" spans="2:45" ht="15" customHeight="1">
@@ -2791,10 +2785,10 @@
         <v>1</v>
       </c>
       <c r="C14" s="24">
-        <f t="shared" si="24"/>
+        <f t="shared" si="23"/>
         <v>45996</v>
       </c>
-      <c r="D14" s="57" t="str">
+      <c r="D14" s="47" t="str">
         <f t="shared" si="10"/>
         <v>金</v>
       </c>
@@ -2842,65 +2836,61 @@
         <f t="shared" si="16"/>
         <v/>
       </c>
-      <c r="AB14" s="55"/>
-      <c r="AC14" s="56">
+      <c r="AB14" s="45"/>
+      <c r="AC14" s="46">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AD14" s="56">
+      <c r="AD14" s="46">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AE14" s="56">
+      <c r="AE14" s="46">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="AF14" s="56">
+      <c r="AF14" s="46">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AG14" s="56">
+      <c r="AG14" s="46">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AH14" s="56">
+      <c r="AH14" s="46">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AI14" s="56">
+      <c r="AI14" s="46">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="AJ14" s="56">
+      <c r="AJ14" s="46">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="AK14" s="56">
+      <c r="AK14" s="46">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AL14" s="56">
+      <c r="AL14" s="46">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="AM14" s="63">
+      <c r="AM14" s="51">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AN14" s="64">
+      <c r="AN14" s="52">
         <f t="shared" si="21"/>
         <v>0.33333333333333331</v>
       </c>
-      <c r="AO14" s="64">
+      <c r="AO14" s="52">
         <f t="shared" si="22"/>
         <v>0.33333333333333331</v>
       </c>
       <c r="AQ14" s="1">
         <v>5</v>
-      </c>
-      <c r="AR14" s="1" t="str">
-        <f t="shared" si="23"/>
-        <v>2025/2/24</v>
       </c>
     </row>
     <row r="15" spans="2:45" ht="15" customHeight="1">
@@ -2909,10 +2899,10 @@
         <v>0</v>
       </c>
       <c r="C15" s="24">
-        <f t="shared" si="24"/>
+        <f t="shared" si="23"/>
         <v>45997</v>
       </c>
-      <c r="D15" s="57" t="str">
+      <c r="D15" s="47" t="str">
         <f t="shared" si="10"/>
         <v>土</v>
       </c>
@@ -2960,65 +2950,61 @@
         <f t="shared" si="16"/>
         <v/>
       </c>
-      <c r="AB15" s="55"/>
-      <c r="AC15" s="56">
+      <c r="AB15" s="45"/>
+      <c r="AC15" s="46">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AD15" s="56">
+      <c r="AD15" s="46">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AE15" s="56">
+      <c r="AE15" s="46">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="AF15" s="56">
+      <c r="AF15" s="46">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AG15" s="56">
+      <c r="AG15" s="46">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AH15" s="56">
+      <c r="AH15" s="46">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AI15" s="56">
+      <c r="AI15" s="46">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="AJ15" s="56">
+      <c r="AJ15" s="46">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="AK15" s="56">
+      <c r="AK15" s="46">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AL15" s="56">
+      <c r="AL15" s="46">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="AM15" s="63">
+      <c r="AM15" s="51">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AN15" s="64">
+      <c r="AN15" s="52">
         <f t="shared" si="21"/>
         <v>0.33333333333333331</v>
       </c>
-      <c r="AO15" s="64">
+      <c r="AO15" s="52">
         <f t="shared" si="22"/>
         <v>0.33333333333333331</v>
       </c>
       <c r="AQ15" s="1">
         <v>6</v>
-      </c>
-      <c r="AR15" s="1" t="str">
-        <f t="shared" si="23"/>
-        <v>2025/3/20</v>
       </c>
     </row>
     <row r="16" spans="2:45" ht="15" customHeight="1">
@@ -3027,10 +3013,10 @@
         <v>0</v>
       </c>
       <c r="C16" s="24">
-        <f t="shared" si="24"/>
+        <f t="shared" si="23"/>
         <v>45998</v>
       </c>
-      <c r="D16" s="57" t="str">
+      <c r="D16" s="47" t="str">
         <f t="shared" si="10"/>
         <v>日</v>
       </c>
@@ -3078,77 +3064,73 @@
         <f t="shared" si="16"/>
         <v/>
       </c>
-      <c r="AB16" s="55"/>
-      <c r="AC16" s="56">
+      <c r="AB16" s="45"/>
+      <c r="AC16" s="46">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AD16" s="56">
+      <c r="AD16" s="46">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AE16" s="56">
+      <c r="AE16" s="46">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="AF16" s="56">
+      <c r="AF16" s="46">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AG16" s="56">
+      <c r="AG16" s="46">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AH16" s="56">
+      <c r="AH16" s="46">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AI16" s="56">
+      <c r="AI16" s="46">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="AJ16" s="56">
+      <c r="AJ16" s="46">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="AK16" s="56">
+      <c r="AK16" s="46">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AL16" s="56">
+      <c r="AL16" s="46">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="AM16" s="63">
+      <c r="AM16" s="51">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AN16" s="64">
+      <c r="AN16" s="52">
         <f t="shared" si="21"/>
         <v>0.33333333333333331</v>
       </c>
-      <c r="AO16" s="64">
+      <c r="AO16" s="52">
         <f t="shared" si="22"/>
         <v>0.33333333333333331</v>
       </c>
       <c r="AQ16" s="1">
         <v>7</v>
       </c>
-      <c r="AR16" s="1" t="str">
-        <f t="shared" si="23"/>
-        <v>2025/4/29</v>
-      </c>
     </row>
-    <row r="17" spans="2:44" ht="15" customHeight="1">
+    <row r="17" spans="2:43" ht="15" customHeight="1">
       <c r="B17" s="23">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="C17" s="24">
-        <f t="shared" si="24"/>
+        <f t="shared" si="23"/>
         <v>45999</v>
       </c>
-      <c r="D17" s="57" t="str">
+      <c r="D17" s="47" t="str">
         <f t="shared" si="10"/>
         <v>月</v>
       </c>
@@ -3196,77 +3178,73 @@
         <f t="shared" si="16"/>
         <v/>
       </c>
-      <c r="AB17" s="55"/>
-      <c r="AC17" s="56">
+      <c r="AB17" s="45"/>
+      <c r="AC17" s="46">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AD17" s="56">
+      <c r="AD17" s="46">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AE17" s="56">
+      <c r="AE17" s="46">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="AF17" s="56">
+      <c r="AF17" s="46">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AG17" s="56">
+      <c r="AG17" s="46">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AH17" s="56">
+      <c r="AH17" s="46">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AI17" s="56">
+      <c r="AI17" s="46">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="AJ17" s="56">
+      <c r="AJ17" s="46">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="AK17" s="56">
+      <c r="AK17" s="46">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AL17" s="56">
+      <c r="AL17" s="46">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="AM17" s="63">
+      <c r="AM17" s="51">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AN17" s="64">
+      <c r="AN17" s="52">
         <f t="shared" si="21"/>
         <v>0.33333333333333331</v>
       </c>
-      <c r="AO17" s="64">
+      <c r="AO17" s="52">
         <f t="shared" si="22"/>
         <v>0.33333333333333331</v>
       </c>
       <c r="AQ17" s="1">
         <v>8</v>
       </c>
-      <c r="AR17" s="1" t="str">
-        <f t="shared" si="23"/>
-        <v>2025/5/3</v>
-      </c>
     </row>
-    <row r="18" spans="2:44" ht="15" customHeight="1">
+    <row r="18" spans="2:43" ht="15" customHeight="1">
       <c r="B18" s="23">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="C18" s="24">
-        <f t="shared" si="24"/>
+        <f t="shared" si="23"/>
         <v>46000</v>
       </c>
-      <c r="D18" s="57" t="str">
+      <c r="D18" s="47" t="str">
         <f t="shared" si="10"/>
         <v>火</v>
       </c>
@@ -3314,77 +3292,73 @@
         <f t="shared" si="16"/>
         <v/>
       </c>
-      <c r="AB18" s="55"/>
-      <c r="AC18" s="56">
+      <c r="AB18" s="45"/>
+      <c r="AC18" s="46">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AD18" s="56">
+      <c r="AD18" s="46">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AE18" s="56">
+      <c r="AE18" s="46">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="AF18" s="56">
+      <c r="AF18" s="46">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AG18" s="56">
+      <c r="AG18" s="46">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AH18" s="56">
+      <c r="AH18" s="46">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AI18" s="56">
+      <c r="AI18" s="46">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="AJ18" s="56">
+      <c r="AJ18" s="46">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="AK18" s="56">
+      <c r="AK18" s="46">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AL18" s="56">
+      <c r="AL18" s="46">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="AM18" s="63">
+      <c r="AM18" s="51">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AN18" s="64">
+      <c r="AN18" s="52">
         <f t="shared" si="21"/>
         <v>0.33333333333333331</v>
       </c>
-      <c r="AO18" s="64">
+      <c r="AO18" s="52">
         <f t="shared" si="22"/>
         <v>0.33333333333333331</v>
       </c>
       <c r="AQ18" s="1">
         <v>9</v>
       </c>
-      <c r="AR18" s="1" t="str">
-        <f t="shared" si="23"/>
-        <v>2025/5/4</v>
-      </c>
     </row>
-    <row r="19" spans="2:44" ht="15" customHeight="1">
+    <row r="19" spans="2:43" ht="15" customHeight="1">
       <c r="B19" s="23">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="C19" s="24">
-        <f t="shared" si="24"/>
+        <f t="shared" si="23"/>
         <v>46001</v>
       </c>
-      <c r="D19" s="57" t="str">
+      <c r="D19" s="47" t="str">
         <f t="shared" si="10"/>
         <v>水</v>
       </c>
@@ -3432,77 +3406,73 @@
         <f t="shared" si="16"/>
         <v/>
       </c>
-      <c r="AB19" s="55"/>
-      <c r="AC19" s="56">
+      <c r="AB19" s="45"/>
+      <c r="AC19" s="46">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AD19" s="56">
+      <c r="AD19" s="46">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AE19" s="56">
+      <c r="AE19" s="46">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="AF19" s="56">
+      <c r="AF19" s="46">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AG19" s="56">
+      <c r="AG19" s="46">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AH19" s="56">
+      <c r="AH19" s="46">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AI19" s="56">
+      <c r="AI19" s="46">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="AJ19" s="56">
+      <c r="AJ19" s="46">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="AK19" s="56">
+      <c r="AK19" s="46">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AL19" s="56">
+      <c r="AL19" s="46">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="AM19" s="63">
+      <c r="AM19" s="51">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AN19" s="64">
+      <c r="AN19" s="52">
         <f t="shared" si="21"/>
         <v>0.33333333333333331</v>
       </c>
-      <c r="AO19" s="64">
+      <c r="AO19" s="52">
         <f t="shared" si="22"/>
         <v>0.33333333333333331</v>
       </c>
       <c r="AQ19" s="1">
         <v>10</v>
       </c>
-      <c r="AR19" s="1" t="str">
-        <f t="shared" si="23"/>
-        <v>2025/5/5</v>
-      </c>
     </row>
-    <row r="20" spans="2:44" ht="15" customHeight="1">
+    <row r="20" spans="2:43" ht="15" customHeight="1">
       <c r="B20" s="23">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="C20" s="24">
-        <f t="shared" si="24"/>
+        <f t="shared" si="23"/>
         <v>46002</v>
       </c>
-      <c r="D20" s="57" t="str">
+      <c r="D20" s="47" t="str">
         <f t="shared" si="10"/>
         <v>木</v>
       </c>
@@ -3550,77 +3520,73 @@
         <f t="shared" si="16"/>
         <v/>
       </c>
-      <c r="AB20" s="55"/>
-      <c r="AC20" s="56">
+      <c r="AB20" s="45"/>
+      <c r="AC20" s="46">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AD20" s="56">
+      <c r="AD20" s="46">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AE20" s="56">
+      <c r="AE20" s="46">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="AF20" s="56">
+      <c r="AF20" s="46">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AG20" s="56">
+      <c r="AG20" s="46">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AH20" s="56">
+      <c r="AH20" s="46">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AI20" s="56">
+      <c r="AI20" s="46">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="AJ20" s="56">
+      <c r="AJ20" s="46">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="AK20" s="56">
+      <c r="AK20" s="46">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AL20" s="56">
+      <c r="AL20" s="46">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="AM20" s="63">
+      <c r="AM20" s="51">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AN20" s="64">
+      <c r="AN20" s="52">
         <f t="shared" si="21"/>
         <v>0.33333333333333331</v>
       </c>
-      <c r="AO20" s="64">
+      <c r="AO20" s="52">
         <f t="shared" si="22"/>
         <v>0.33333333333333331</v>
       </c>
       <c r="AQ20" s="1">
         <v>11</v>
       </c>
-      <c r="AR20" s="1" t="str">
-        <f t="shared" si="23"/>
-        <v>2025/5/6</v>
-      </c>
     </row>
-    <row r="21" spans="2:44" ht="15" customHeight="1">
+    <row r="21" spans="2:43" ht="15" customHeight="1">
       <c r="B21" s="23">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="C21" s="24">
-        <f t="shared" si="24"/>
+        <f t="shared" si="23"/>
         <v>46003</v>
       </c>
-      <c r="D21" s="57" t="str">
+      <c r="D21" s="47" t="str">
         <f t="shared" si="10"/>
         <v>金</v>
       </c>
@@ -3668,77 +3634,73 @@
         <f t="shared" si="16"/>
         <v/>
       </c>
-      <c r="AB21" s="55"/>
-      <c r="AC21" s="56">
+      <c r="AB21" s="45"/>
+      <c r="AC21" s="46">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AD21" s="56">
+      <c r="AD21" s="46">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AE21" s="56">
+      <c r="AE21" s="46">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="AF21" s="56">
+      <c r="AF21" s="46">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AG21" s="56">
+      <c r="AG21" s="46">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AH21" s="56">
+      <c r="AH21" s="46">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AI21" s="56">
+      <c r="AI21" s="46">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="AJ21" s="56">
+      <c r="AJ21" s="46">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="AK21" s="56">
+      <c r="AK21" s="46">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AL21" s="56">
+      <c r="AL21" s="46">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="AM21" s="63">
+      <c r="AM21" s="51">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AN21" s="64">
+      <c r="AN21" s="52">
         <f t="shared" si="21"/>
         <v>0.33333333333333331</v>
       </c>
-      <c r="AO21" s="64">
+      <c r="AO21" s="52">
         <f t="shared" si="22"/>
         <v>0.33333333333333331</v>
       </c>
       <c r="AQ21" s="1">
         <v>12</v>
       </c>
-      <c r="AR21" s="1" t="str">
-        <f t="shared" si="23"/>
-        <v>2025/7/21</v>
-      </c>
     </row>
-    <row r="22" spans="2:44" ht="15" customHeight="1">
+    <row r="22" spans="2:43" ht="15" customHeight="1">
       <c r="B22" s="23">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="C22" s="24">
-        <f t="shared" si="24"/>
+        <f t="shared" si="23"/>
         <v>46004</v>
       </c>
-      <c r="D22" s="57" t="str">
+      <c r="D22" s="47" t="str">
         <f t="shared" si="10"/>
         <v>土</v>
       </c>
@@ -3786,77 +3748,73 @@
         <f t="shared" si="16"/>
         <v/>
       </c>
-      <c r="AB22" s="55"/>
-      <c r="AC22" s="56">
+      <c r="AB22" s="45"/>
+      <c r="AC22" s="46">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AD22" s="56">
+      <c r="AD22" s="46">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AE22" s="56">
+      <c r="AE22" s="46">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="AF22" s="56">
+      <c r="AF22" s="46">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AG22" s="56">
+      <c r="AG22" s="46">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AH22" s="56">
+      <c r="AH22" s="46">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AI22" s="56">
+      <c r="AI22" s="46">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="AJ22" s="56">
+      <c r="AJ22" s="46">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="AK22" s="56">
+      <c r="AK22" s="46">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AL22" s="56">
+      <c r="AL22" s="46">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="AM22" s="63">
+      <c r="AM22" s="51">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AN22" s="64">
+      <c r="AN22" s="52">
         <f t="shared" si="21"/>
         <v>0.33333333333333331</v>
       </c>
-      <c r="AO22" s="64">
+      <c r="AO22" s="52">
         <f t="shared" si="22"/>
         <v>0.33333333333333331</v>
       </c>
       <c r="AQ22" s="1">
         <v>13</v>
       </c>
-      <c r="AR22" s="1" t="str">
-        <f t="shared" si="23"/>
-        <v>2025/8/11</v>
-      </c>
     </row>
-    <row r="23" spans="2:44" ht="15" customHeight="1">
+    <row r="23" spans="2:43" ht="15" customHeight="1">
       <c r="B23" s="23">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="C23" s="24">
-        <f t="shared" si="24"/>
+        <f t="shared" si="23"/>
         <v>46005</v>
       </c>
-      <c r="D23" s="57" t="str">
+      <c r="D23" s="47" t="str">
         <f t="shared" si="10"/>
         <v>日</v>
       </c>
@@ -3904,77 +3862,73 @@
         <f t="shared" si="16"/>
         <v/>
       </c>
-      <c r="AB23" s="55"/>
-      <c r="AC23" s="56">
+      <c r="AB23" s="45"/>
+      <c r="AC23" s="46">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AD23" s="56">
+      <c r="AD23" s="46">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AE23" s="56">
+      <c r="AE23" s="46">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="AF23" s="56">
+      <c r="AF23" s="46">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AG23" s="56">
+      <c r="AG23" s="46">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AH23" s="56">
+      <c r="AH23" s="46">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AI23" s="56">
+      <c r="AI23" s="46">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="AJ23" s="56">
+      <c r="AJ23" s="46">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="AK23" s="56">
+      <c r="AK23" s="46">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AL23" s="56">
+      <c r="AL23" s="46">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="AM23" s="63">
+      <c r="AM23" s="51">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AN23" s="64">
+      <c r="AN23" s="52">
         <f t="shared" si="21"/>
         <v>0.33333333333333331</v>
       </c>
-      <c r="AO23" s="64">
+      <c r="AO23" s="52">
         <f t="shared" si="22"/>
         <v>0.33333333333333331</v>
       </c>
       <c r="AQ23" s="1">
         <v>14</v>
       </c>
-      <c r="AR23" s="1" t="str">
-        <f t="shared" si="23"/>
-        <v>2025/9/15</v>
-      </c>
     </row>
-    <row r="24" spans="2:44" ht="15" customHeight="1">
+    <row r="24" spans="2:43" ht="15" customHeight="1">
       <c r="B24" s="23">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="C24" s="24">
-        <f t="shared" si="24"/>
+        <f t="shared" si="23"/>
         <v>46006</v>
       </c>
-      <c r="D24" s="57" t="str">
+      <c r="D24" s="47" t="str">
         <f t="shared" si="10"/>
         <v>月</v>
       </c>
@@ -4022,77 +3976,73 @@
         <f t="shared" si="16"/>
         <v/>
       </c>
-      <c r="AB24" s="55"/>
-      <c r="AC24" s="56">
+      <c r="AB24" s="45"/>
+      <c r="AC24" s="46">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AD24" s="56">
+      <c r="AD24" s="46">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AE24" s="56">
+      <c r="AE24" s="46">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="AF24" s="56">
+      <c r="AF24" s="46">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AG24" s="56">
+      <c r="AG24" s="46">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AH24" s="56">
+      <c r="AH24" s="46">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AI24" s="56">
+      <c r="AI24" s="46">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="AJ24" s="56">
+      <c r="AJ24" s="46">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="AK24" s="56">
+      <c r="AK24" s="46">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AL24" s="56">
+      <c r="AL24" s="46">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="AM24" s="63">
+      <c r="AM24" s="51">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AN24" s="64">
+      <c r="AN24" s="52">
         <f t="shared" si="21"/>
         <v>0.33333333333333331</v>
       </c>
-      <c r="AO24" s="64">
+      <c r="AO24" s="52">
         <f t="shared" si="22"/>
         <v>0.33333333333333331</v>
       </c>
       <c r="AQ24" s="1">
         <v>15</v>
       </c>
-      <c r="AR24" s="1" t="str">
-        <f t="shared" si="23"/>
-        <v>2025/9/23</v>
-      </c>
     </row>
-    <row r="25" spans="2:44" ht="15" customHeight="1">
+    <row r="25" spans="2:43" ht="15" customHeight="1">
       <c r="B25" s="23">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="C25" s="24">
-        <f t="shared" si="24"/>
+        <f t="shared" si="23"/>
         <v>46007</v>
       </c>
-      <c r="D25" s="57" t="str">
+      <c r="D25" s="47" t="str">
         <f t="shared" si="10"/>
         <v>火</v>
       </c>
@@ -4140,77 +4090,73 @@
         <f t="shared" si="16"/>
         <v/>
       </c>
-      <c r="AB25" s="55"/>
-      <c r="AC25" s="56">
+      <c r="AB25" s="45"/>
+      <c r="AC25" s="46">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AD25" s="56">
+      <c r="AD25" s="46">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AE25" s="56">
+      <c r="AE25" s="46">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="AF25" s="56">
+      <c r="AF25" s="46">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AG25" s="56">
+      <c r="AG25" s="46">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AH25" s="56">
+      <c r="AH25" s="46">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AI25" s="56">
+      <c r="AI25" s="46">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="AJ25" s="56">
+      <c r="AJ25" s="46">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="AK25" s="56">
+      <c r="AK25" s="46">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AL25" s="56">
+      <c r="AL25" s="46">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="AM25" s="63">
+      <c r="AM25" s="51">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AN25" s="64">
+      <c r="AN25" s="52">
         <f t="shared" si="21"/>
         <v>0.33333333333333331</v>
       </c>
-      <c r="AO25" s="64">
+      <c r="AO25" s="52">
         <f t="shared" si="22"/>
         <v>0.33333333333333331</v>
       </c>
       <c r="AQ25" s="1">
         <v>16</v>
       </c>
-      <c r="AR25" s="1" t="str">
-        <f t="shared" si="23"/>
-        <v>2025/10/13</v>
-      </c>
     </row>
-    <row r="26" spans="2:44" ht="15" customHeight="1">
+    <row r="26" spans="2:43" ht="15" customHeight="1">
       <c r="B26" s="23">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="C26" s="24">
-        <f t="shared" si="24"/>
+        <f t="shared" si="23"/>
         <v>46008</v>
       </c>
-      <c r="D26" s="57" t="str">
+      <c r="D26" s="47" t="str">
         <f t="shared" si="10"/>
         <v>水</v>
       </c>
@@ -4258,77 +4204,73 @@
         <f t="shared" si="16"/>
         <v/>
       </c>
-      <c r="AB26" s="55"/>
-      <c r="AC26" s="56">
+      <c r="AB26" s="45"/>
+      <c r="AC26" s="46">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AD26" s="56">
+      <c r="AD26" s="46">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AE26" s="56">
+      <c r="AE26" s="46">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="AF26" s="56">
+      <c r="AF26" s="46">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AG26" s="56">
+      <c r="AG26" s="46">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AH26" s="56">
+      <c r="AH26" s="46">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AI26" s="56">
+      <c r="AI26" s="46">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="AJ26" s="56">
+      <c r="AJ26" s="46">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="AK26" s="56">
+      <c r="AK26" s="46">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AL26" s="56">
+      <c r="AL26" s="46">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="AM26" s="63">
+      <c r="AM26" s="51">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AN26" s="64">
+      <c r="AN26" s="52">
         <f t="shared" si="21"/>
         <v>0.33333333333333331</v>
       </c>
-      <c r="AO26" s="64">
+      <c r="AO26" s="52">
         <f t="shared" si="22"/>
         <v>0.33333333333333331</v>
       </c>
       <c r="AQ26" s="1">
         <v>17</v>
       </c>
-      <c r="AR26" s="1" t="str">
-        <f t="shared" si="23"/>
-        <v>2025/11/3</v>
-      </c>
     </row>
-    <row r="27" spans="2:44" ht="15" customHeight="1">
+    <row r="27" spans="2:43" ht="15" customHeight="1">
       <c r="B27" s="23">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="C27" s="24">
-        <f t="shared" si="24"/>
+        <f t="shared" si="23"/>
         <v>46009</v>
       </c>
-      <c r="D27" s="57" t="str">
+      <c r="D27" s="47" t="str">
         <f t="shared" si="10"/>
         <v>木</v>
       </c>
@@ -4376,77 +4318,73 @@
         <f t="shared" si="16"/>
         <v/>
       </c>
-      <c r="AB27" s="55"/>
-      <c r="AC27" s="56">
+      <c r="AB27" s="45"/>
+      <c r="AC27" s="46">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AD27" s="56">
+      <c r="AD27" s="46">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AE27" s="56">
+      <c r="AE27" s="46">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="AF27" s="56">
+      <c r="AF27" s="46">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AG27" s="56">
+      <c r="AG27" s="46">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AH27" s="56">
+      <c r="AH27" s="46">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AI27" s="56">
+      <c r="AI27" s="46">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="AJ27" s="56">
+      <c r="AJ27" s="46">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="AK27" s="56">
+      <c r="AK27" s="46">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AL27" s="56">
+      <c r="AL27" s="46">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="AM27" s="63">
+      <c r="AM27" s="51">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AN27" s="64">
+      <c r="AN27" s="52">
         <f t="shared" si="21"/>
         <v>0.33333333333333331</v>
       </c>
-      <c r="AO27" s="64">
+      <c r="AO27" s="52">
         <f t="shared" si="22"/>
         <v>0.33333333333333331</v>
       </c>
       <c r="AQ27" s="1">
         <v>18</v>
       </c>
-      <c r="AR27" s="1" t="str">
-        <f t="shared" si="23"/>
-        <v>2025/11/23</v>
-      </c>
     </row>
-    <row r="28" spans="2:44" ht="15" customHeight="1">
+    <row r="28" spans="2:43" ht="15" customHeight="1">
       <c r="B28" s="23">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="C28" s="24">
-        <f t="shared" si="24"/>
+        <f t="shared" si="23"/>
         <v>46010</v>
       </c>
-      <c r="D28" s="57" t="str">
+      <c r="D28" s="47" t="str">
         <f t="shared" si="10"/>
         <v>金</v>
       </c>
@@ -4494,77 +4432,73 @@
         <f t="shared" si="16"/>
         <v/>
       </c>
-      <c r="AB28" s="55"/>
-      <c r="AC28" s="56">
+      <c r="AB28" s="45"/>
+      <c r="AC28" s="46">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AD28" s="56">
+      <c r="AD28" s="46">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AE28" s="56">
+      <c r="AE28" s="46">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="AF28" s="56">
+      <c r="AF28" s="46">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AG28" s="56">
+      <c r="AG28" s="46">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AH28" s="56">
+      <c r="AH28" s="46">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AI28" s="56">
+      <c r="AI28" s="46">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="AJ28" s="56">
+      <c r="AJ28" s="46">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="AK28" s="56">
+      <c r="AK28" s="46">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AL28" s="56">
+      <c r="AL28" s="46">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="AM28" s="63">
+      <c r="AM28" s="51">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AN28" s="64">
+      <c r="AN28" s="52">
         <f t="shared" si="21"/>
         <v>0.33333333333333331</v>
       </c>
-      <c r="AO28" s="64">
+      <c r="AO28" s="52">
         <f t="shared" si="22"/>
         <v>0.33333333333333331</v>
       </c>
       <c r="AQ28" s="1">
         <v>19</v>
       </c>
-      <c r="AR28" s="1" t="str">
-        <f t="shared" si="23"/>
-        <v>2025/11/24</v>
-      </c>
     </row>
-    <row r="29" spans="2:44" ht="15" customHeight="1">
+    <row r="29" spans="2:43" ht="15" customHeight="1">
       <c r="B29" s="23">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="C29" s="24">
-        <f t="shared" si="24"/>
+        <f t="shared" si="23"/>
         <v>46011</v>
       </c>
-      <c r="D29" s="57" t="str">
+      <c r="D29" s="47" t="str">
         <f t="shared" si="10"/>
         <v>土</v>
       </c>
@@ -4612,77 +4546,73 @@
         <f t="shared" si="16"/>
         <v/>
       </c>
-      <c r="AB29" s="55"/>
-      <c r="AC29" s="56">
+      <c r="AB29" s="45"/>
+      <c r="AC29" s="46">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AD29" s="56">
+      <c r="AD29" s="46">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AE29" s="56">
+      <c r="AE29" s="46">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="AF29" s="56">
+      <c r="AF29" s="46">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AG29" s="56">
+      <c r="AG29" s="46">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AH29" s="56">
+      <c r="AH29" s="46">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AI29" s="56">
+      <c r="AI29" s="46">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="AJ29" s="56">
+      <c r="AJ29" s="46">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="AK29" s="56">
+      <c r="AK29" s="46">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AL29" s="56">
+      <c r="AL29" s="46">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="AM29" s="63">
+      <c r="AM29" s="51">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AN29" s="64">
+      <c r="AN29" s="52">
         <f t="shared" si="21"/>
         <v>0.33333333333333331</v>
       </c>
-      <c r="AO29" s="64">
+      <c r="AO29" s="52">
         <f t="shared" si="22"/>
         <v>0.33333333333333331</v>
       </c>
       <c r="AQ29" s="1">
         <v>20</v>
       </c>
-      <c r="AR29" s="1" t="str">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
     </row>
-    <row r="30" spans="2:44" ht="15" customHeight="1">
+    <row r="30" spans="2:43" ht="15" customHeight="1">
       <c r="B30" s="23">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="C30" s="24">
-        <f t="shared" si="24"/>
+        <f t="shared" si="23"/>
         <v>46012</v>
       </c>
-      <c r="D30" s="57" t="str">
+      <c r="D30" s="47" t="str">
         <f t="shared" si="10"/>
         <v>日</v>
       </c>
@@ -4730,77 +4660,73 @@
         <f t="shared" si="16"/>
         <v/>
       </c>
-      <c r="AB30" s="55"/>
-      <c r="AC30" s="56">
+      <c r="AB30" s="45"/>
+      <c r="AC30" s="46">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AD30" s="56">
+      <c r="AD30" s="46">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AE30" s="56">
+      <c r="AE30" s="46">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="AF30" s="56">
+      <c r="AF30" s="46">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AG30" s="56">
+      <c r="AG30" s="46">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AH30" s="56">
+      <c r="AH30" s="46">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AI30" s="56">
+      <c r="AI30" s="46">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="AJ30" s="56">
+      <c r="AJ30" s="46">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="AK30" s="56">
+      <c r="AK30" s="46">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AL30" s="56">
+      <c r="AL30" s="46">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="AM30" s="63">
+      <c r="AM30" s="51">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AN30" s="64">
+      <c r="AN30" s="52">
         <f t="shared" si="21"/>
         <v>0.33333333333333331</v>
       </c>
-      <c r="AO30" s="64">
+      <c r="AO30" s="52">
         <f t="shared" si="22"/>
         <v>0.33333333333333331</v>
       </c>
       <c r="AQ30" s="1">
         <v>21</v>
       </c>
-      <c r="AR30" s="1" t="str">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
     </row>
-    <row r="31" spans="2:44" ht="15" customHeight="1">
+    <row r="31" spans="2:43" ht="15" customHeight="1">
       <c r="B31" s="23">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="C31" s="24">
-        <f t="shared" si="24"/>
+        <f t="shared" si="23"/>
         <v>46013</v>
       </c>
-      <c r="D31" s="57" t="str">
+      <c r="D31" s="47" t="str">
         <f t="shared" si="10"/>
         <v>月</v>
       </c>
@@ -4848,77 +4774,73 @@
         <f t="shared" si="16"/>
         <v/>
       </c>
-      <c r="AB31" s="55"/>
-      <c r="AC31" s="56">
+      <c r="AB31" s="45"/>
+      <c r="AC31" s="46">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AD31" s="56">
+      <c r="AD31" s="46">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AE31" s="56">
+      <c r="AE31" s="46">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="AF31" s="56">
+      <c r="AF31" s="46">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AG31" s="56">
+      <c r="AG31" s="46">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AH31" s="56">
+      <c r="AH31" s="46">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AI31" s="56">
+      <c r="AI31" s="46">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="AJ31" s="56">
+      <c r="AJ31" s="46">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="AK31" s="56">
+      <c r="AK31" s="46">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AL31" s="56">
+      <c r="AL31" s="46">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="AM31" s="63">
+      <c r="AM31" s="51">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AN31" s="64">
+      <c r="AN31" s="52">
         <f t="shared" si="21"/>
         <v>0.33333333333333331</v>
       </c>
-      <c r="AO31" s="64">
+      <c r="AO31" s="52">
         <f t="shared" si="22"/>
         <v>0.33333333333333331</v>
       </c>
       <c r="AQ31" s="1">
         <v>22</v>
       </c>
-      <c r="AR31" s="1" t="str">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
     </row>
-    <row r="32" spans="2:44" ht="15" customHeight="1">
+    <row r="32" spans="2:43" ht="15" customHeight="1">
       <c r="B32" s="23">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="C32" s="24">
-        <f t="shared" si="24"/>
+        <f t="shared" si="23"/>
         <v>46014</v>
       </c>
-      <c r="D32" s="57" t="str">
+      <c r="D32" s="47" t="str">
         <f t="shared" si="10"/>
         <v>火</v>
       </c>
@@ -4966,77 +4888,73 @@
         <f t="shared" si="16"/>
         <v/>
       </c>
-      <c r="AB32" s="55"/>
-      <c r="AC32" s="56">
+      <c r="AB32" s="45"/>
+      <c r="AC32" s="46">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AD32" s="56">
+      <c r="AD32" s="46">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AE32" s="56">
+      <c r="AE32" s="46">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="AF32" s="56">
+      <c r="AF32" s="46">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AG32" s="56">
+      <c r="AG32" s="46">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AH32" s="56">
+      <c r="AH32" s="46">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AI32" s="56">
+      <c r="AI32" s="46">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="AJ32" s="56">
+      <c r="AJ32" s="46">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="AK32" s="56">
+      <c r="AK32" s="46">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AL32" s="56">
+      <c r="AL32" s="46">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="AM32" s="63">
+      <c r="AM32" s="51">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AN32" s="64">
+      <c r="AN32" s="52">
         <f t="shared" si="21"/>
         <v>0.33333333333333331</v>
       </c>
-      <c r="AO32" s="64">
+      <c r="AO32" s="52">
         <f t="shared" si="22"/>
         <v>0.33333333333333331</v>
       </c>
       <c r="AQ32" s="1">
         <v>23</v>
       </c>
-      <c r="AR32" s="1" t="str">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
     </row>
-    <row r="33" spans="2:44" ht="15" customHeight="1">
+    <row r="33" spans="2:43" ht="15" customHeight="1">
       <c r="B33" s="23">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="C33" s="24">
-        <f t="shared" si="24"/>
+        <f t="shared" si="23"/>
         <v>46015</v>
       </c>
-      <c r="D33" s="57" t="str">
+      <c r="D33" s="47" t="str">
         <f t="shared" si="10"/>
         <v>水</v>
       </c>
@@ -5084,77 +5002,73 @@
         <f t="shared" si="16"/>
         <v/>
       </c>
-      <c r="AB33" s="55"/>
-      <c r="AC33" s="56">
+      <c r="AB33" s="45"/>
+      <c r="AC33" s="46">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AD33" s="56">
+      <c r="AD33" s="46">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AE33" s="56">
+      <c r="AE33" s="46">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="AF33" s="56">
+      <c r="AF33" s="46">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AG33" s="56">
+      <c r="AG33" s="46">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AH33" s="56">
+      <c r="AH33" s="46">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AI33" s="56">
+      <c r="AI33" s="46">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="AJ33" s="56">
+      <c r="AJ33" s="46">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="AK33" s="56">
+      <c r="AK33" s="46">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AL33" s="56">
+      <c r="AL33" s="46">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="AM33" s="63">
+      <c r="AM33" s="51">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AN33" s="64">
+      <c r="AN33" s="52">
         <f t="shared" si="21"/>
         <v>0.33333333333333331</v>
       </c>
-      <c r="AO33" s="64">
+      <c r="AO33" s="52">
         <f t="shared" si="22"/>
         <v>0.33333333333333331</v>
       </c>
       <c r="AQ33" s="1">
         <v>24</v>
       </c>
-      <c r="AR33" s="1" t="str">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
     </row>
-    <row r="34" spans="2:44" ht="15" customHeight="1">
+    <row r="34" spans="2:43" ht="15" customHeight="1">
       <c r="B34" s="23">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="C34" s="24">
-        <f t="shared" si="24"/>
+        <f t="shared" si="23"/>
         <v>46016</v>
       </c>
-      <c r="D34" s="57" t="str">
+      <c r="D34" s="47" t="str">
         <f t="shared" si="10"/>
         <v>木</v>
       </c>
@@ -5202,77 +5116,73 @@
         <f t="shared" si="16"/>
         <v/>
       </c>
-      <c r="AB34" s="55"/>
-      <c r="AC34" s="56">
+      <c r="AB34" s="45"/>
+      <c r="AC34" s="46">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AD34" s="56">
+      <c r="AD34" s="46">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AE34" s="56">
+      <c r="AE34" s="46">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="AF34" s="56">
+      <c r="AF34" s="46">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AG34" s="56">
+      <c r="AG34" s="46">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AH34" s="56">
+      <c r="AH34" s="46">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AI34" s="56">
+      <c r="AI34" s="46">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="AJ34" s="56">
+      <c r="AJ34" s="46">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="AK34" s="56">
+      <c r="AK34" s="46">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AL34" s="56">
+      <c r="AL34" s="46">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="AM34" s="63">
+      <c r="AM34" s="51">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AN34" s="64">
+      <c r="AN34" s="52">
         <f t="shared" si="21"/>
         <v>0.33333333333333331</v>
       </c>
-      <c r="AO34" s="64">
+      <c r="AO34" s="52">
         <f t="shared" si="22"/>
         <v>0.33333333333333331</v>
       </c>
       <c r="AQ34" s="1">
         <v>25</v>
       </c>
-      <c r="AR34" s="1" t="str">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
     </row>
-    <row r="35" spans="2:44" ht="15" customHeight="1">
+    <row r="35" spans="2:43" ht="15" customHeight="1">
       <c r="B35" s="23">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="C35" s="24">
-        <f t="shared" si="24"/>
+        <f t="shared" si="23"/>
         <v>46017</v>
       </c>
-      <c r="D35" s="57" t="str">
+      <c r="D35" s="47" t="str">
         <f t="shared" si="10"/>
         <v>金</v>
       </c>
@@ -5320,77 +5230,73 @@
         <f t="shared" si="16"/>
         <v/>
       </c>
-      <c r="AB35" s="55"/>
-      <c r="AC35" s="56">
+      <c r="AB35" s="45"/>
+      <c r="AC35" s="46">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AD35" s="56">
+      <c r="AD35" s="46">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AE35" s="56">
+      <c r="AE35" s="46">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="AF35" s="56">
+      <c r="AF35" s="46">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AG35" s="56">
+      <c r="AG35" s="46">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AH35" s="56">
+      <c r="AH35" s="46">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AI35" s="56">
+      <c r="AI35" s="46">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="AJ35" s="56">
+      <c r="AJ35" s="46">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="AK35" s="56">
+      <c r="AK35" s="46">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AL35" s="56">
+      <c r="AL35" s="46">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="AM35" s="63">
+      <c r="AM35" s="51">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AN35" s="64">
+      <c r="AN35" s="52">
         <f t="shared" si="21"/>
         <v>0.33333333333333331</v>
       </c>
-      <c r="AO35" s="64">
+      <c r="AO35" s="52">
         <f t="shared" si="22"/>
         <v>0.33333333333333331</v>
       </c>
       <c r="AQ35" s="1">
         <v>26</v>
       </c>
-      <c r="AR35" s="1" t="str">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
     </row>
-    <row r="36" spans="2:44" ht="15" customHeight="1">
+    <row r="36" spans="2:43" ht="15" customHeight="1">
       <c r="B36" s="23">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="C36" s="24">
-        <f t="shared" si="24"/>
+        <f t="shared" si="23"/>
         <v>46018</v>
       </c>
-      <c r="D36" s="57" t="str">
+      <c r="D36" s="47" t="str">
         <f t="shared" si="10"/>
         <v>土</v>
       </c>
@@ -5438,77 +5344,73 @@
         <f t="shared" si="16"/>
         <v/>
       </c>
-      <c r="AB36" s="55"/>
-      <c r="AC36" s="56">
+      <c r="AB36" s="45"/>
+      <c r="AC36" s="46">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AD36" s="56">
+      <c r="AD36" s="46">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AE36" s="56">
+      <c r="AE36" s="46">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="AF36" s="56">
+      <c r="AF36" s="46">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AG36" s="56">
+      <c r="AG36" s="46">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AH36" s="56">
+      <c r="AH36" s="46">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AI36" s="56">
+      <c r="AI36" s="46">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="AJ36" s="56">
+      <c r="AJ36" s="46">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="AK36" s="56">
+      <c r="AK36" s="46">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AL36" s="56">
+      <c r="AL36" s="46">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="AM36" s="63">
+      <c r="AM36" s="51">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AN36" s="64">
+      <c r="AN36" s="52">
         <f t="shared" si="21"/>
         <v>0.33333333333333331</v>
       </c>
-      <c r="AO36" s="64">
+      <c r="AO36" s="52">
         <f t="shared" si="22"/>
         <v>0.33333333333333331</v>
       </c>
       <c r="AQ36" s="1">
         <v>27</v>
       </c>
-      <c r="AR36" s="1" t="str">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
     </row>
-    <row r="37" spans="2:44" ht="15" customHeight="1">
+    <row r="37" spans="2:43" ht="15" customHeight="1">
       <c r="B37" s="23">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="C37" s="24">
-        <f t="shared" si="24"/>
+        <f t="shared" si="23"/>
         <v>46019</v>
       </c>
-      <c r="D37" s="57" t="str">
+      <c r="D37" s="47" t="str">
         <f t="shared" si="10"/>
         <v>日</v>
       </c>
@@ -5556,77 +5458,73 @@
         <f t="shared" si="16"/>
         <v/>
       </c>
-      <c r="AB37" s="55"/>
-      <c r="AC37" s="56">
+      <c r="AB37" s="45"/>
+      <c r="AC37" s="46">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AD37" s="56">
+      <c r="AD37" s="46">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AE37" s="56">
+      <c r="AE37" s="46">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="AF37" s="56">
+      <c r="AF37" s="46">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AG37" s="56">
+      <c r="AG37" s="46">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AH37" s="56">
+      <c r="AH37" s="46">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AI37" s="56">
+      <c r="AI37" s="46">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="AJ37" s="56">
+      <c r="AJ37" s="46">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="AK37" s="56">
+      <c r="AK37" s="46">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AL37" s="56">
+      <c r="AL37" s="46">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="AM37" s="63">
+      <c r="AM37" s="51">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AN37" s="64">
+      <c r="AN37" s="52">
         <f t="shared" si="21"/>
         <v>0.33333333333333331</v>
       </c>
-      <c r="AO37" s="64">
+      <c r="AO37" s="52">
         <f t="shared" si="22"/>
         <v>0.33333333333333331</v>
       </c>
       <c r="AQ37" s="1">
         <v>28</v>
       </c>
-      <c r="AR37" s="1" t="str">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
     </row>
-    <row r="38" spans="2:44" ht="15" customHeight="1">
+    <row r="38" spans="2:43" ht="15" customHeight="1">
       <c r="B38" s="23">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="C38" s="24">
-        <f t="shared" si="24"/>
+        <f t="shared" si="23"/>
         <v>46020</v>
       </c>
-      <c r="D38" s="57" t="str">
+      <c r="D38" s="47" t="str">
         <f t="shared" si="10"/>
         <v>月</v>
       </c>
@@ -5674,77 +5572,73 @@
         <f t="shared" si="16"/>
         <v/>
       </c>
-      <c r="AB38" s="55"/>
-      <c r="AC38" s="56">
+      <c r="AB38" s="45"/>
+      <c r="AC38" s="46">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AD38" s="56">
+      <c r="AD38" s="46">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AE38" s="56">
+      <c r="AE38" s="46">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="AF38" s="56">
+      <c r="AF38" s="46">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AG38" s="56">
+      <c r="AG38" s="46">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AH38" s="56">
+      <c r="AH38" s="46">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AI38" s="56">
+      <c r="AI38" s="46">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="AJ38" s="56">
+      <c r="AJ38" s="46">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="AK38" s="56">
+      <c r="AK38" s="46">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AL38" s="56">
+      <c r="AL38" s="46">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="AM38" s="63">
+      <c r="AM38" s="51">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AN38" s="64">
+      <c r="AN38" s="52">
         <f t="shared" si="21"/>
         <v>0.33333333333333331</v>
       </c>
-      <c r="AO38" s="64">
+      <c r="AO38" s="52">
         <f t="shared" si="22"/>
         <v>0.33333333333333331</v>
       </c>
       <c r="AQ38" s="1">
         <v>29</v>
       </c>
-      <c r="AR38" s="1" t="str">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
     </row>
-    <row r="39" spans="2:44" ht="15" customHeight="1">
+    <row r="39" spans="2:43" ht="15" customHeight="1">
       <c r="B39" s="23">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="C39" s="24">
-        <f t="shared" si="24"/>
+        <f t="shared" si="23"/>
         <v>46021</v>
       </c>
-      <c r="D39" s="57" t="str">
+      <c r="D39" s="47" t="str">
         <f t="shared" si="10"/>
         <v>火</v>
       </c>
@@ -5792,68 +5686,64 @@
         <f t="shared" si="16"/>
         <v/>
       </c>
-      <c r="AB39" s="55"/>
-      <c r="AC39" s="56">
+      <c r="AB39" s="45"/>
+      <c r="AC39" s="46">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AD39" s="56">
+      <c r="AD39" s="46">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AE39" s="56">
+      <c r="AE39" s="46">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="AF39" s="56">
+      <c r="AF39" s="46">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AG39" s="56">
+      <c r="AG39" s="46">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AH39" s="56">
+      <c r="AH39" s="46">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AI39" s="56">
+      <c r="AI39" s="46">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="AJ39" s="56">
+      <c r="AJ39" s="46">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="AK39" s="56">
+      <c r="AK39" s="46">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AL39" s="56">
+      <c r="AL39" s="46">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="AM39" s="63">
+      <c r="AM39" s="51">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AN39" s="64">
+      <c r="AN39" s="52">
         <f t="shared" si="21"/>
         <v>0.33333333333333331</v>
       </c>
-      <c r="AO39" s="64">
+      <c r="AO39" s="52">
         <f t="shared" si="22"/>
         <v>0.33333333333333331</v>
       </c>
       <c r="AQ39" s="1">
         <v>30</v>
       </c>
-      <c r="AR39" s="1" t="str">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
     </row>
-    <row r="40" spans="2:44" ht="15" customHeight="1">
+    <row r="40" spans="2:43" ht="15" customHeight="1">
       <c r="B40" s="23">
         <f t="shared" si="9"/>
         <v>1</v>
@@ -5862,7 +5752,7 @@
         <f>IFERROR(IF(AND(ISNUMBER(C39), MONTH(C39+1) = MONTH($C$10), C39+1 &lt;= EOMONTH($C$10, 0)), C39+1, ""), "")</f>
         <v>46022</v>
       </c>
-      <c r="D40" s="57" t="str">
+      <c r="D40" s="47" t="str">
         <f t="shared" si="10"/>
         <v>水</v>
       </c>
@@ -5910,68 +5800,64 @@
         <f t="shared" si="16"/>
         <v/>
       </c>
-      <c r="AB40" s="55"/>
-      <c r="AC40" s="56">
+      <c r="AB40" s="45"/>
+      <c r="AC40" s="46">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AD40" s="56">
+      <c r="AD40" s="46">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AE40" s="56">
+      <c r="AE40" s="46">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="AF40" s="56">
+      <c r="AF40" s="46">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AG40" s="56">
+      <c r="AG40" s="46">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AH40" s="56">
+      <c r="AH40" s="46">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AI40" s="56">
+      <c r="AI40" s="46">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="AJ40" s="56">
+      <c r="AJ40" s="46">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="AK40" s="56">
+      <c r="AK40" s="46">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AL40" s="56">
+      <c r="AL40" s="46">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="AM40" s="63">
+      <c r="AM40" s="51">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AN40" s="64">
+      <c r="AN40" s="52">
         <f t="shared" si="21"/>
         <v>0.33333333333333331</v>
       </c>
-      <c r="AO40" s="64">
+      <c r="AO40" s="52">
         <f t="shared" si="22"/>
         <v>0.33333333333333331</v>
       </c>
       <c r="AQ40" s="1">
         <v>31</v>
       </c>
-      <c r="AR40" s="1" t="str">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
     </row>
-    <row r="41" spans="2:44" ht="30" customHeight="1">
+    <row r="41" spans="2:43" ht="30" customHeight="1">
       <c r="B41" s="29" t="s">
         <v>48</v>
       </c>
@@ -6000,55 +5886,55 @@
         <v>0</v>
       </c>
       <c r="O41" s="33">
-        <f t="shared" ref="O41:U41" si="25">COUNTIF(O10:O40, "○")</f>
+        <f t="shared" ref="O41:U41" si="24">COUNTIF(O10:O40, "○")</f>
         <v>0</v>
       </c>
       <c r="P41" s="33">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="Q41" s="33">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="R41" s="33">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="S41" s="33">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="T41" s="33">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="U41" s="33">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="V41" s="70">
+        <f t="shared" ref="V41:AA41" si="25">SUM(V10:V40)</f>
+        <v>0</v>
+      </c>
+      <c r="W41" s="70">
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="Q41" s="33">
+      <c r="X41" s="70">
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="R41" s="33">
+      <c r="Y41" s="70">
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="S41" s="33">
+      <c r="Z41" s="70">
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="T41" s="33">
+      <c r="AA41" s="70">
         <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="U41" s="33">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="V41" s="95">
-        <f t="shared" ref="V41:AA41" si="26">SUM(V10:V40)</f>
-        <v>0</v>
-      </c>
-      <c r="W41" s="95">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="X41" s="95">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="Y41" s="95">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="Z41" s="95">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="AA41" s="95">
-        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="AB41" s="35"/>
@@ -6063,7 +5949,7 @@
       <c r="AK41" s="35"/>
       <c r="AL41" s="36"/>
     </row>
-    <row r="42" spans="2:44" ht="32.1" customHeight="1">
+    <row r="42" spans="2:43" ht="32" customHeight="1">
       <c r="B42" s="37"/>
       <c r="D42" s="38"/>
       <c r="E42" s="38"/>
@@ -6089,7 +5975,7 @@
       <c r="Y42" s="36"/>
       <c r="Z42" s="36"/>
     </row>
-    <row r="43" spans="2:44" ht="33.950000000000003" customHeight="1" thickBot="1">
+    <row r="43" spans="2:43" ht="34" customHeight="1" thickBot="1">
       <c r="B43" s="39" t="s">
         <v>49</v>
       </c>
@@ -6099,132 +5985,132 @@
       <c r="Y43" s="36"/>
       <c r="Z43" s="36"/>
     </row>
-    <row r="44" spans="2:44">
+    <row r="44" spans="2:43">
       <c r="B44" s="40"/>
       <c r="C44" s="40"/>
-      <c r="D44" s="107" t="s">
+      <c r="D44" s="82" t="s">
         <v>50</v>
       </c>
-      <c r="E44" s="107" t="s">
+      <c r="E44" s="82" t="s">
         <v>51</v>
       </c>
-      <c r="F44" s="108" t="s">
+      <c r="F44" s="83" t="s">
         <v>52</v>
       </c>
-      <c r="G44" s="108" t="s">
+      <c r="G44" s="83" t="s">
         <v>53</v>
       </c>
-      <c r="H44" s="108" t="s">
+      <c r="H44" s="83" t="s">
         <v>54</v>
       </c>
-      <c r="I44" s="109" t="s">
+      <c r="I44" s="84" t="s">
         <v>55</v>
       </c>
-      <c r="J44" s="108" t="s">
+      <c r="J44" s="83" t="s">
         <v>56</v>
       </c>
-      <c r="K44" s="108" t="s">
+      <c r="K44" s="83" t="s">
         <v>57</v>
       </c>
-      <c r="L44" s="108" t="s">
+      <c r="L44" s="83" t="s">
         <v>58</v>
       </c>
-      <c r="M44" s="108" t="s">
+      <c r="M44" s="83" t="s">
         <v>59</v>
       </c>
-      <c r="N44" s="108" t="s">
+      <c r="N44" s="83" t="s">
         <v>60</v>
       </c>
-      <c r="O44" s="108" t="s">
+      <c r="O44" s="83" t="s">
         <v>61</v>
       </c>
-      <c r="P44" s="108" t="s">
+      <c r="P44" s="83" t="s">
         <v>62</v>
       </c>
-      <c r="Q44" s="109" t="s">
+      <c r="Q44" s="84" t="s">
         <v>63</v>
       </c>
-      <c r="R44" s="109" t="s">
+      <c r="R44" s="84" t="s">
         <v>64</v>
       </c>
-      <c r="S44" s="109" t="s">
+      <c r="S44" s="84" t="s">
         <v>65</v>
       </c>
-      <c r="T44" s="108" t="s">
+      <c r="T44" s="83" t="s">
         <v>66</v>
       </c>
-      <c r="U44" s="108" t="s">
+      <c r="U44" s="83" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="45" spans="2:44">
+    <row r="45" spans="2:43">
       <c r="B45" s="38"/>
       <c r="C45" s="38"/>
-      <c r="D45" s="103" t="str">
+      <c r="D45" s="78" t="str">
         <f>TEXT(D4,"000000")</f>
         <v>000000</v>
       </c>
-      <c r="E45" s="103">
+      <c r="E45" s="78">
         <f>D5</f>
         <v>0</v>
       </c>
-      <c r="F45" s="104">
+      <c r="F45" s="79">
         <f>N41</f>
         <v>0</v>
       </c>
-      <c r="G45" s="104">
+      <c r="G45" s="79">
         <f>O41</f>
         <v>0</v>
       </c>
-      <c r="H45" s="104" t="str">
+      <c r="H45" s="79" t="str">
         <f>IF(OR(ISBLANK(U41), U41=0), "*", U41)</f>
         <v>*</v>
       </c>
-      <c r="I45" s="104" t="s">
+      <c r="I45" s="79" t="s">
         <v>68</v>
       </c>
-      <c r="J45" s="105" t="str" cm="1">
+      <c r="J45" s="80" t="str" cm="1">
         <f t="array" ref="J45">IF(AND(OR(ISBLANK(P41), P41=0), OR(ISBLANK(SUMPRODUCT(--(ISNUMBER(K8:K40))*(K8:K40&lt;&gt;0))), SUMPRODUCT(--(ISNUMBER(K8:K40))*(K8:K40&lt;&gt;0))=0)), "*", P41 + (SUMPRODUCT(--(ISNUMBER(K8:K40))*(K8:K40&lt;&gt;0)) / 2))</f>
         <v>*</v>
       </c>
-      <c r="K45" s="104" t="str">
+      <c r="K45" s="79" t="str">
         <f>IF(OR(ISBLANK(Q41), Q41=0), "*", Q41)</f>
         <v>*</v>
       </c>
-      <c r="L45" s="104" t="str">
+      <c r="L45" s="79" t="str">
         <f>IF(OR(ISBLANK(R41), R41=0), "*", R41)</f>
         <v>*</v>
       </c>
-      <c r="M45" s="106" t="str">
+      <c r="M45" s="81" t="str">
         <f>IF(OR(ISBLANK(V41), V41&lt;=0), "*", VALUE(V41))</f>
         <v>*</v>
       </c>
-      <c r="N45" s="106" t="str">
+      <c r="N45" s="81" t="str">
         <f>IF(OR(W41&lt;=0, ROUND(VALUE(W41)-"10:00", 8)&lt;=0),"*",VALUE(W41)-"10:00")</f>
         <v>*</v>
       </c>
-      <c r="O45" s="106" t="str">
+      <c r="O45" s="81" t="str">
         <f>IF(MIN(X41,ROUND(IF(N45="*",0,N45)+IF(P45="*",0,P45),8))=0,"*",MIN(X41,ROUND(IF(N45="*",0,N45)+IF(P45="*",0,P45),8)))</f>
         <v>*</v>
       </c>
-      <c r="P45" s="106" t="str">
+      <c r="P45" s="81" t="str">
         <f>IF(ROUND(MAX(0,Y41-MAX(0,"10:00"-(W41&gt;0)*W41)),8)&lt;=0,"*",MAX(0,Y41-MAX(0,"10:00"-(W41&gt;0)*W41)))</f>
         <v>*</v>
       </c>
-      <c r="Q45" s="104" t="s">
+      <c r="Q45" s="79" t="s">
         <v>68</v>
       </c>
-      <c r="R45" s="104" t="s">
+      <c r="R45" s="79" t="s">
         <v>68</v>
       </c>
-      <c r="S45" s="104" t="s">
+      <c r="S45" s="79" t="s">
         <v>68</v>
       </c>
-      <c r="T45" s="104" t="str">
+      <c r="T45" s="79" t="str">
         <f>IF(COUNTIF(L10:M40, "&lt;&gt;")=0, "*", IF(COUNTIF(L10:M40, 0)&gt;0, "*", COUNTIF(L10:M40, "&lt;&gt;")))</f>
         <v>*</v>
       </c>
-      <c r="U45" s="106" t="str">
+      <c r="U45" s="81" t="str">
         <f>IF(OR(ISBLANK(Z41+AA41), (Z41+AA41)&lt;=0), "*", VALUE(Z41+AA41))</f>
         <v>*</v>
       </c>
@@ -6266,7 +6152,7 @@
       <formula>AE10&gt;=1.000001</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="4">
+  <dataValidations count="9">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2" xr:uid="{F7178D89-8198-DC4E-B6E5-4275518BB33E}">
       <formula1>"ユーニスイースト,ユーニスウエスト"</formula1>
     </dataValidation>
@@ -6279,6 +6165,23 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I2" xr:uid="{F87989B7-3635-A244-A9ED-66AAF34B04D6}">
       <formula1>"東京支社,名古屋支社,大阪支社"</formula1>
     </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O2" xr:uid="{FC3F328D-635A-496C-9900-E56143AA62A6}">
+      <formula1>"1,2,3,4,5,6,7,8,9,10,11,12"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D3" xr:uid="{9CA8B60E-4AB5-4C5B-900D-2714AF060D61}">
+      <formula1>"1,2,3,4,5"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K3" xr:uid="{4311093D-8F41-4975-A814-A09135CA7049}">
+      <formula1>"1,2,3,4,5"</formula1>
+    </dataValidation>
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D4" xr:uid="{55238C5F-FD40-45B8-B9F3-409443BDADA8}">
+      <formula1>0</formula1>
+      <formula2>9999999999</formula2>
+    </dataValidation>
+    <dataValidation type="time" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J4" xr:uid="{029AFA8F-43DE-4722-825C-C116DC441F2E}">
+      <formula1>0</formula1>
+      <formula2>1</formula2>
+    </dataValidation>
   </dataValidations>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="61" orientation="portrait" r:id="rId1"/>

--- a/src/main/resources/2025年10月度UNISS勤務表(〇〇).xlsx
+++ b/src/main/resources/2025年10月度UNISS勤務表(〇〇).xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/akihirokakutani/Documents/GitHub/Kotlin_SpringBoot/src/main/resources/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/akihirokakutani/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0D47118-4F28-934A-AF7E-DCDA7419FAD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5400705-085F-B146-80A4-E4DE0CE8B3A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="620" windowWidth="29040" windowHeight="15720" xr2:uid="{5FD4C467-C22C-E24D-BDF3-40761EFBB2C5}"/>
   </bookViews>
@@ -75,7 +75,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -2325,7 +2325,7 @@
     </row>
     <row r="10" spans="2:45" ht="15" customHeight="1">
       <c r="B10" s="23">
-        <f>IFERROR(IF(OR(COUNTIF($AR$10:$AR$40, C10)&gt;0, WEEKDAY(C10, 2)&gt;5), 0, 1), "")</f>
+        <f ca="1">IFERROR(IF(OR(COUNTIF($AR$10:$AR$40, C10)&gt;0, WEEKDAY(C10, 2)&gt;5), 0, 1), "")</f>
         <v>1</v>
       </c>
       <c r="C10" s="24">
@@ -2436,10 +2436,14 @@
       <c r="AQ10" s="1">
         <v>1</v>
       </c>
+      <c r="AR10" s="1" t="str">
+        <f ca="1">IF(M$2="", "年度を入力してください", IFERROR(_xlfn.WEBSERVICE("https://api.excelapi.org/datetime/holiday-list?year="&amp;M$2&amp;"&amp;line="&amp;$AQ10), "祝日が読み取れません。手入力でお願いします。"))</f>
+        <v>祝日が読み取れません。手入力でお願いします。</v>
+      </c>
     </row>
     <row r="11" spans="2:45" ht="15" customHeight="1">
       <c r="B11" s="23">
-        <f t="shared" ref="B11:B40" si="9">IFERROR(IF(OR(COUNTIF($AR$10:$AR$40, C11)&gt;0, WEEKDAY(C11, 2)&gt;5), 0, 1), "")</f>
+        <f t="shared" ref="B11:B40" ca="1" si="9">IFERROR(IF(OR(COUNTIF($AR$10:$AR$40, C11)&gt;0, WEEKDAY(C11, 2)&gt;5), 0, 1), "")</f>
         <v>1</v>
       </c>
       <c r="C11" s="24">
@@ -2550,14 +2554,18 @@
       <c r="AQ11" s="1">
         <v>2</v>
       </c>
+      <c r="AR11" s="1" t="str">
+        <f t="shared" ref="AR11:AR40" ca="1" si="23">IF(M$2="", "", IFERROR(_xlfn.WEBSERVICE("https://api.excelapi.org/datetime/holiday-list?year="&amp;M$2&amp;"&amp;line="&amp;$AQ11), ""))</f>
+        <v/>
+      </c>
     </row>
     <row r="12" spans="2:45" ht="15" customHeight="1">
       <c r="B12" s="23">
-        <f t="shared" si="9"/>
+        <f t="shared" ca="1" si="9"/>
         <v>1</v>
       </c>
       <c r="C12" s="24">
-        <f t="shared" ref="C12:C39" si="23">IFERROR(IF(AND(ISNUMBER(C11), MONTH(C11+1) = MONTH($C$10), C11+1 &lt;= EOMONTH($C$10, 0)), C11+1, ""), "")</f>
+        <f t="shared" ref="C12:C39" si="24">IFERROR(IF(AND(ISNUMBER(C11), MONTH(C11+1) = MONTH($C$10), C11+1 &lt;= EOMONTH($C$10, 0)), C11+1, ""), "")</f>
         <v>45994</v>
       </c>
       <c r="D12" s="47" t="str">
@@ -2664,14 +2672,18 @@
       <c r="AQ12" s="1">
         <v>3</v>
       </c>
+      <c r="AR12" s="1" t="str">
+        <f t="shared" ca="1" si="23"/>
+        <v/>
+      </c>
     </row>
     <row r="13" spans="2:45" ht="15" customHeight="1">
       <c r="B13" s="23">
-        <f t="shared" si="9"/>
+        <f t="shared" ca="1" si="9"/>
         <v>1</v>
       </c>
       <c r="C13" s="24">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>45995</v>
       </c>
       <c r="D13" s="47" t="str">
@@ -2778,14 +2790,18 @@
       <c r="AQ13" s="1">
         <v>4</v>
       </c>
+      <c r="AR13" s="1" t="str">
+        <f t="shared" ca="1" si="23"/>
+        <v/>
+      </c>
     </row>
     <row r="14" spans="2:45" ht="15" customHeight="1">
       <c r="B14" s="23">
-        <f t="shared" si="9"/>
+        <f t="shared" ca="1" si="9"/>
         <v>1</v>
       </c>
       <c r="C14" s="24">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>45996</v>
       </c>
       <c r="D14" s="47" t="str">
@@ -2892,14 +2908,18 @@
       <c r="AQ14" s="1">
         <v>5</v>
       </c>
+      <c r="AR14" s="1" t="str">
+        <f t="shared" ca="1" si="23"/>
+        <v/>
+      </c>
     </row>
     <row r="15" spans="2:45" ht="15" customHeight="1">
       <c r="B15" s="23">
-        <f t="shared" si="9"/>
+        <f t="shared" ca="1" si="9"/>
         <v>0</v>
       </c>
       <c r="C15" s="24">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>45997</v>
       </c>
       <c r="D15" s="47" t="str">
@@ -3006,14 +3026,18 @@
       <c r="AQ15" s="1">
         <v>6</v>
       </c>
+      <c r="AR15" s="1" t="str">
+        <f t="shared" ca="1" si="23"/>
+        <v/>
+      </c>
     </row>
     <row r="16" spans="2:45" ht="15" customHeight="1">
       <c r="B16" s="23">
-        <f t="shared" si="9"/>
+        <f t="shared" ca="1" si="9"/>
         <v>0</v>
       </c>
       <c r="C16" s="24">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>45998</v>
       </c>
       <c r="D16" s="47" t="str">
@@ -3120,14 +3144,18 @@
       <c r="AQ16" s="1">
         <v>7</v>
       </c>
+      <c r="AR16" s="1" t="str">
+        <f t="shared" ca="1" si="23"/>
+        <v/>
+      </c>
     </row>
-    <row r="17" spans="2:43" ht="15" customHeight="1">
+    <row r="17" spans="2:44" ht="15" customHeight="1">
       <c r="B17" s="23">
-        <f t="shared" si="9"/>
+        <f t="shared" ca="1" si="9"/>
         <v>1</v>
       </c>
       <c r="C17" s="24">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>45999</v>
       </c>
       <c r="D17" s="47" t="str">
@@ -3234,14 +3262,18 @@
       <c r="AQ17" s="1">
         <v>8</v>
       </c>
+      <c r="AR17" s="1" t="str">
+        <f t="shared" ca="1" si="23"/>
+        <v/>
+      </c>
     </row>
-    <row r="18" spans="2:43" ht="15" customHeight="1">
+    <row r="18" spans="2:44" ht="15" customHeight="1">
       <c r="B18" s="23">
-        <f t="shared" si="9"/>
+        <f t="shared" ca="1" si="9"/>
         <v>1</v>
       </c>
       <c r="C18" s="24">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>46000</v>
       </c>
       <c r="D18" s="47" t="str">
@@ -3348,14 +3380,18 @@
       <c r="AQ18" s="1">
         <v>9</v>
       </c>
+      <c r="AR18" s="1" t="str">
+        <f t="shared" ca="1" si="23"/>
+        <v/>
+      </c>
     </row>
-    <row r="19" spans="2:43" ht="15" customHeight="1">
+    <row r="19" spans="2:44" ht="15" customHeight="1">
       <c r="B19" s="23">
-        <f t="shared" si="9"/>
+        <f t="shared" ca="1" si="9"/>
         <v>1</v>
       </c>
       <c r="C19" s="24">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>46001</v>
       </c>
       <c r="D19" s="47" t="str">
@@ -3462,14 +3498,18 @@
       <c r="AQ19" s="1">
         <v>10</v>
       </c>
+      <c r="AR19" s="1" t="str">
+        <f t="shared" ca="1" si="23"/>
+        <v/>
+      </c>
     </row>
-    <row r="20" spans="2:43" ht="15" customHeight="1">
+    <row r="20" spans="2:44" ht="15" customHeight="1">
       <c r="B20" s="23">
-        <f t="shared" si="9"/>
+        <f t="shared" ca="1" si="9"/>
         <v>1</v>
       </c>
       <c r="C20" s="24">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>46002</v>
       </c>
       <c r="D20" s="47" t="str">
@@ -3576,14 +3616,18 @@
       <c r="AQ20" s="1">
         <v>11</v>
       </c>
+      <c r="AR20" s="1" t="str">
+        <f t="shared" ca="1" si="23"/>
+        <v/>
+      </c>
     </row>
-    <row r="21" spans="2:43" ht="15" customHeight="1">
+    <row r="21" spans="2:44" ht="15" customHeight="1">
       <c r="B21" s="23">
-        <f t="shared" si="9"/>
+        <f t="shared" ca="1" si="9"/>
         <v>1</v>
       </c>
       <c r="C21" s="24">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>46003</v>
       </c>
       <c r="D21" s="47" t="str">
@@ -3690,14 +3734,18 @@
       <c r="AQ21" s="1">
         <v>12</v>
       </c>
+      <c r="AR21" s="1" t="str">
+        <f t="shared" ca="1" si="23"/>
+        <v/>
+      </c>
     </row>
-    <row r="22" spans="2:43" ht="15" customHeight="1">
+    <row r="22" spans="2:44" ht="15" customHeight="1">
       <c r="B22" s="23">
-        <f t="shared" si="9"/>
+        <f t="shared" ca="1" si="9"/>
         <v>0</v>
       </c>
       <c r="C22" s="24">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>46004</v>
       </c>
       <c r="D22" s="47" t="str">
@@ -3804,14 +3852,18 @@
       <c r="AQ22" s="1">
         <v>13</v>
       </c>
+      <c r="AR22" s="1" t="str">
+        <f t="shared" ca="1" si="23"/>
+        <v/>
+      </c>
     </row>
-    <row r="23" spans="2:43" ht="15" customHeight="1">
+    <row r="23" spans="2:44" ht="15" customHeight="1">
       <c r="B23" s="23">
-        <f t="shared" si="9"/>
+        <f t="shared" ca="1" si="9"/>
         <v>0</v>
       </c>
       <c r="C23" s="24">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>46005</v>
       </c>
       <c r="D23" s="47" t="str">
@@ -3918,14 +3970,18 @@
       <c r="AQ23" s="1">
         <v>14</v>
       </c>
+      <c r="AR23" s="1" t="str">
+        <f t="shared" ca="1" si="23"/>
+        <v/>
+      </c>
     </row>
-    <row r="24" spans="2:43" ht="15" customHeight="1">
+    <row r="24" spans="2:44" ht="15" customHeight="1">
       <c r="B24" s="23">
-        <f t="shared" si="9"/>
+        <f t="shared" ca="1" si="9"/>
         <v>1</v>
       </c>
       <c r="C24" s="24">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>46006</v>
       </c>
       <c r="D24" s="47" t="str">
@@ -4032,14 +4088,18 @@
       <c r="AQ24" s="1">
         <v>15</v>
       </c>
+      <c r="AR24" s="1" t="str">
+        <f t="shared" ca="1" si="23"/>
+        <v/>
+      </c>
     </row>
-    <row r="25" spans="2:43" ht="15" customHeight="1">
+    <row r="25" spans="2:44" ht="15" customHeight="1">
       <c r="B25" s="23">
-        <f t="shared" si="9"/>
+        <f t="shared" ca="1" si="9"/>
         <v>1</v>
       </c>
       <c r="C25" s="24">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>46007</v>
       </c>
       <c r="D25" s="47" t="str">
@@ -4146,14 +4206,18 @@
       <c r="AQ25" s="1">
         <v>16</v>
       </c>
+      <c r="AR25" s="1" t="str">
+        <f t="shared" ca="1" si="23"/>
+        <v/>
+      </c>
     </row>
-    <row r="26" spans="2:43" ht="15" customHeight="1">
+    <row r="26" spans="2:44" ht="15" customHeight="1">
       <c r="B26" s="23">
-        <f t="shared" si="9"/>
+        <f t="shared" ca="1" si="9"/>
         <v>1</v>
       </c>
       <c r="C26" s="24">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>46008</v>
       </c>
       <c r="D26" s="47" t="str">
@@ -4260,14 +4324,18 @@
       <c r="AQ26" s="1">
         <v>17</v>
       </c>
+      <c r="AR26" s="1" t="str">
+        <f t="shared" ca="1" si="23"/>
+        <v/>
+      </c>
     </row>
-    <row r="27" spans="2:43" ht="15" customHeight="1">
+    <row r="27" spans="2:44" ht="15" customHeight="1">
       <c r="B27" s="23">
-        <f t="shared" si="9"/>
+        <f t="shared" ca="1" si="9"/>
         <v>1</v>
       </c>
       <c r="C27" s="24">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>46009</v>
       </c>
       <c r="D27" s="47" t="str">
@@ -4374,14 +4442,18 @@
       <c r="AQ27" s="1">
         <v>18</v>
       </c>
+      <c r="AR27" s="1" t="str">
+        <f t="shared" ca="1" si="23"/>
+        <v/>
+      </c>
     </row>
-    <row r="28" spans="2:43" ht="15" customHeight="1">
+    <row r="28" spans="2:44" ht="15" customHeight="1">
       <c r="B28" s="23">
-        <f t="shared" si="9"/>
+        <f t="shared" ca="1" si="9"/>
         <v>1</v>
       </c>
       <c r="C28" s="24">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>46010</v>
       </c>
       <c r="D28" s="47" t="str">
@@ -4488,14 +4560,18 @@
       <c r="AQ28" s="1">
         <v>19</v>
       </c>
+      <c r="AR28" s="1" t="str">
+        <f t="shared" ca="1" si="23"/>
+        <v/>
+      </c>
     </row>
-    <row r="29" spans="2:43" ht="15" customHeight="1">
+    <row r="29" spans="2:44" ht="15" customHeight="1">
       <c r="B29" s="23">
-        <f t="shared" si="9"/>
+        <f t="shared" ca="1" si="9"/>
         <v>0</v>
       </c>
       <c r="C29" s="24">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>46011</v>
       </c>
       <c r="D29" s="47" t="str">
@@ -4602,14 +4678,18 @@
       <c r="AQ29" s="1">
         <v>20</v>
       </c>
+      <c r="AR29" s="1" t="str">
+        <f t="shared" ca="1" si="23"/>
+        <v/>
+      </c>
     </row>
-    <row r="30" spans="2:43" ht="15" customHeight="1">
+    <row r="30" spans="2:44" ht="15" customHeight="1">
       <c r="B30" s="23">
-        <f t="shared" si="9"/>
+        <f t="shared" ca="1" si="9"/>
         <v>0</v>
       </c>
       <c r="C30" s="24">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>46012</v>
       </c>
       <c r="D30" s="47" t="str">
@@ -4716,14 +4796,18 @@
       <c r="AQ30" s="1">
         <v>21</v>
       </c>
+      <c r="AR30" s="1" t="str">
+        <f t="shared" ca="1" si="23"/>
+        <v/>
+      </c>
     </row>
-    <row r="31" spans="2:43" ht="15" customHeight="1">
+    <row r="31" spans="2:44" ht="15" customHeight="1">
       <c r="B31" s="23">
-        <f t="shared" si="9"/>
+        <f t="shared" ca="1" si="9"/>
         <v>1</v>
       </c>
       <c r="C31" s="24">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>46013</v>
       </c>
       <c r="D31" s="47" t="str">
@@ -4830,14 +4914,18 @@
       <c r="AQ31" s="1">
         <v>22</v>
       </c>
+      <c r="AR31" s="1" t="str">
+        <f t="shared" ca="1" si="23"/>
+        <v/>
+      </c>
     </row>
-    <row r="32" spans="2:43" ht="15" customHeight="1">
+    <row r="32" spans="2:44" ht="15" customHeight="1">
       <c r="B32" s="23">
-        <f t="shared" si="9"/>
+        <f t="shared" ca="1" si="9"/>
         <v>1</v>
       </c>
       <c r="C32" s="24">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>46014</v>
       </c>
       <c r="D32" s="47" t="str">
@@ -4944,14 +5032,18 @@
       <c r="AQ32" s="1">
         <v>23</v>
       </c>
+      <c r="AR32" s="1" t="str">
+        <f t="shared" ca="1" si="23"/>
+        <v/>
+      </c>
     </row>
-    <row r="33" spans="2:43" ht="15" customHeight="1">
+    <row r="33" spans="2:44" ht="15" customHeight="1">
       <c r="B33" s="23">
-        <f t="shared" si="9"/>
+        <f t="shared" ca="1" si="9"/>
         <v>1</v>
       </c>
       <c r="C33" s="24">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>46015</v>
       </c>
       <c r="D33" s="47" t="str">
@@ -5058,14 +5150,18 @@
       <c r="AQ33" s="1">
         <v>24</v>
       </c>
+      <c r="AR33" s="1" t="str">
+        <f t="shared" ca="1" si="23"/>
+        <v/>
+      </c>
     </row>
-    <row r="34" spans="2:43" ht="15" customHeight="1">
+    <row r="34" spans="2:44" ht="15" customHeight="1">
       <c r="B34" s="23">
-        <f t="shared" si="9"/>
+        <f t="shared" ca="1" si="9"/>
         <v>1</v>
       </c>
       <c r="C34" s="24">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>46016</v>
       </c>
       <c r="D34" s="47" t="str">
@@ -5172,14 +5268,18 @@
       <c r="AQ34" s="1">
         <v>25</v>
       </c>
+      <c r="AR34" s="1" t="str">
+        <f t="shared" ca="1" si="23"/>
+        <v/>
+      </c>
     </row>
-    <row r="35" spans="2:43" ht="15" customHeight="1">
+    <row r="35" spans="2:44" ht="15" customHeight="1">
       <c r="B35" s="23">
-        <f t="shared" si="9"/>
+        <f t="shared" ca="1" si="9"/>
         <v>1</v>
       </c>
       <c r="C35" s="24">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>46017</v>
       </c>
       <c r="D35" s="47" t="str">
@@ -5286,14 +5386,18 @@
       <c r="AQ35" s="1">
         <v>26</v>
       </c>
+      <c r="AR35" s="1" t="str">
+        <f t="shared" ca="1" si="23"/>
+        <v/>
+      </c>
     </row>
-    <row r="36" spans="2:43" ht="15" customHeight="1">
+    <row r="36" spans="2:44" ht="15" customHeight="1">
       <c r="B36" s="23">
-        <f t="shared" si="9"/>
+        <f t="shared" ca="1" si="9"/>
         <v>0</v>
       </c>
       <c r="C36" s="24">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>46018</v>
       </c>
       <c r="D36" s="47" t="str">
@@ -5400,14 +5504,18 @@
       <c r="AQ36" s="1">
         <v>27</v>
       </c>
+      <c r="AR36" s="1" t="str">
+        <f t="shared" ca="1" si="23"/>
+        <v/>
+      </c>
     </row>
-    <row r="37" spans="2:43" ht="15" customHeight="1">
+    <row r="37" spans="2:44" ht="15" customHeight="1">
       <c r="B37" s="23">
-        <f t="shared" si="9"/>
+        <f t="shared" ca="1" si="9"/>
         <v>0</v>
       </c>
       <c r="C37" s="24">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>46019</v>
       </c>
       <c r="D37" s="47" t="str">
@@ -5514,14 +5622,18 @@
       <c r="AQ37" s="1">
         <v>28</v>
       </c>
+      <c r="AR37" s="1" t="str">
+        <f t="shared" ca="1" si="23"/>
+        <v/>
+      </c>
     </row>
-    <row r="38" spans="2:43" ht="15" customHeight="1">
+    <row r="38" spans="2:44" ht="15" customHeight="1">
       <c r="B38" s="23">
-        <f t="shared" si="9"/>
+        <f t="shared" ca="1" si="9"/>
         <v>1</v>
       </c>
       <c r="C38" s="24">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>46020</v>
       </c>
       <c r="D38" s="47" t="str">
@@ -5628,14 +5740,18 @@
       <c r="AQ38" s="1">
         <v>29</v>
       </c>
+      <c r="AR38" s="1" t="str">
+        <f t="shared" ca="1" si="23"/>
+        <v/>
+      </c>
     </row>
-    <row r="39" spans="2:43" ht="15" customHeight="1">
+    <row r="39" spans="2:44" ht="15" customHeight="1">
       <c r="B39" s="23">
-        <f t="shared" si="9"/>
+        <f t="shared" ca="1" si="9"/>
         <v>1</v>
       </c>
       <c r="C39" s="24">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>46021</v>
       </c>
       <c r="D39" s="47" t="str">
@@ -5742,10 +5858,14 @@
       <c r="AQ39" s="1">
         <v>30</v>
       </c>
+      <c r="AR39" s="1" t="str">
+        <f t="shared" ca="1" si="23"/>
+        <v/>
+      </c>
     </row>
-    <row r="40" spans="2:43" ht="15" customHeight="1">
+    <row r="40" spans="2:44" ht="15" customHeight="1">
       <c r="B40" s="23">
-        <f t="shared" si="9"/>
+        <f t="shared" ca="1" si="9"/>
         <v>1</v>
       </c>
       <c r="C40" s="24">
@@ -5856,8 +5976,12 @@
       <c r="AQ40" s="1">
         <v>31</v>
       </c>
+      <c r="AR40" s="1" t="str">
+        <f t="shared" ca="1" si="23"/>
+        <v/>
+      </c>
     </row>
-    <row r="41" spans="2:43" ht="30" customHeight="1">
+    <row r="41" spans="2:44" ht="30" customHeight="1">
       <c r="B41" s="29" t="s">
         <v>48</v>
       </c>
@@ -5886,55 +6010,55 @@
         <v>0</v>
       </c>
       <c r="O41" s="33">
-        <f t="shared" ref="O41:U41" si="24">COUNTIF(O10:O40, "○")</f>
+        <f t="shared" ref="O41:U41" si="25">COUNTIF(O10:O40, "○")</f>
         <v>0</v>
       </c>
       <c r="P41" s="33">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="Q41" s="33">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="R41" s="33">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="S41" s="33">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="T41" s="33">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="U41" s="33">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="V41" s="70">
-        <f t="shared" ref="V41:AA41" si="25">SUM(V10:V40)</f>
+        <f t="shared" ref="V41:AA41" si="26">SUM(V10:V40)</f>
         <v>0</v>
       </c>
       <c r="W41" s="70">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="X41" s="70">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="Y41" s="70">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="Z41" s="70">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="AA41" s="70">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="AB41" s="35"/>
@@ -5949,7 +6073,7 @@
       <c r="AK41" s="35"/>
       <c r="AL41" s="36"/>
     </row>
-    <row r="42" spans="2:43" ht="32" customHeight="1">
+    <row r="42" spans="2:44" ht="32" customHeight="1">
       <c r="B42" s="37"/>
       <c r="D42" s="38"/>
       <c r="E42" s="38"/>
@@ -5975,7 +6099,7 @@
       <c r="Y42" s="36"/>
       <c r="Z42" s="36"/>
     </row>
-    <row r="43" spans="2:43" ht="34" customHeight="1" thickBot="1">
+    <row r="43" spans="2:44" ht="34" customHeight="1" thickBot="1">
       <c r="B43" s="39" t="s">
         <v>49</v>
       </c>
@@ -5985,7 +6109,7 @@
       <c r="Y43" s="36"/>
       <c r="Z43" s="36"/>
     </row>
-    <row r="44" spans="2:43">
+    <row r="44" spans="2:44">
       <c r="B44" s="40"/>
       <c r="C44" s="40"/>
       <c r="D44" s="82" t="s">
@@ -6043,7 +6167,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="45" spans="2:43">
+    <row r="45" spans="2:44">
       <c r="B45" s="38"/>
       <c r="C45" s="38"/>
       <c r="D45" s="78" t="str">
@@ -6152,7 +6276,7 @@
       <formula>AE10&gt;=1.000001</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="9">
+  <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2" xr:uid="{F7178D89-8198-DC4E-B6E5-4275518BB33E}">
       <formula1>"ユーニスイースト,ユーニスウエスト"</formula1>
     </dataValidation>
@@ -6165,23 +6289,6 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I2" xr:uid="{F87989B7-3635-A244-A9ED-66AAF34B04D6}">
       <formula1>"東京支社,名古屋支社,大阪支社"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O2" xr:uid="{FC3F328D-635A-496C-9900-E56143AA62A6}">
-      <formula1>"1,2,3,4,5,6,7,8,9,10,11,12"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D3" xr:uid="{9CA8B60E-4AB5-4C5B-900D-2714AF060D61}">
-      <formula1>"1,2,3,4,5"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K3" xr:uid="{4311093D-8F41-4975-A814-A09135CA7049}">
-      <formula1>"1,2,3,4,5"</formula1>
-    </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D4" xr:uid="{55238C5F-FD40-45B8-B9F3-409443BDADA8}">
-      <formula1>0</formula1>
-      <formula2>9999999999</formula2>
-    </dataValidation>
-    <dataValidation type="time" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J4" xr:uid="{029AFA8F-43DE-4722-825C-C116DC441F2E}">
-      <formula1>0</formula1>
-      <formula2>1</formula2>
-    </dataValidation>
   </dataValidations>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="61" orientation="portrait" r:id="rId1"/>
